--- a/output/2026-10-09/enriched_analysis.xlsx
+++ b/output/2026-10-09/enriched_analysis.xlsx
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>2.234</v>
+        <v>2.233</v>
       </c>
       <c r="W2" t="n">
-        <v>2820</v>
+        <v>2821</v>
       </c>
       <c r="X2" t="n">
         <v>22.1</v>
@@ -1396,10 +1396,10 @@
         <v>0.046</v>
       </c>
       <c r="W4" t="n">
-        <v>2903</v>
+        <v>2902</v>
       </c>
       <c r="X4" t="n">
-        <v>9.98</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="Y4" t="n">
         <v>36</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>0.137</v>
+        <v>0.136</v>
       </c>
       <c r="W7" t="n">
-        <v>2297</v>
+        <v>2300</v>
       </c>
       <c r="X7" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="Y7" t="n">
         <v>-3</v>
@@ -2319,13 +2319,13 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>1.167</v>
+        <v>1.173</v>
       </c>
       <c r="W8" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="X8" t="n">
-        <v>7.3</v>
+        <v>7.28</v>
       </c>
       <c r="Y8" t="n">
         <v>17</v>
@@ -2551,13 +2551,13 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>1.18</v>
+        <v>1.188</v>
       </c>
       <c r="W9" t="n">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="X9" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Y9" t="n">
         <v>22</v>
@@ -2786,7 +2786,7 @@
         <v>0.048</v>
       </c>
       <c r="W10" t="n">
-        <v>14958</v>
+        <v>14952</v>
       </c>
       <c r="X10" t="n">
         <v>38.1</v>
@@ -3015,13 +3015,13 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>2.338</v>
+        <v>2.348</v>
       </c>
       <c r="W11" t="n">
-        <v>2511</v>
+        <v>2500</v>
       </c>
       <c r="X11" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Y11" t="n">
         <v>6</v>
@@ -3250,10 +3250,10 @@
         <v>0.067</v>
       </c>
       <c r="W12" t="n">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="X12" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="Y12" t="n">
         <v>19</v>
@@ -3477,13 +3477,13 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>0.052</v>
+        <v>0.051</v>
       </c>
       <c r="W13" t="n">
-        <v>1594</v>
+        <v>1602</v>
       </c>
       <c r="X13" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="Y13" t="n">
         <v>55</v>
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>2564</v>
+        <v>2561</v>
       </c>
       <c r="X14" t="n">
         <v>21</v>
@@ -3944,7 +3944,7 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="W15" t="n">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="X15" t="n">
         <v>36.7</v>
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>2.946</v>
+        <v>2.95</v>
       </c>
       <c r="W16" t="n">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="X16" t="n">
         <v>20.2</v>
@@ -4399,13 +4399,13 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>0.193</v>
+        <v>0.188</v>
       </c>
       <c r="W17" t="n">
-        <v>574</v>
+        <v>590</v>
       </c>
       <c r="X17" t="n">
-        <v>48</v>
+        <v>49.3</v>
       </c>
       <c r="Y17" t="n">
         <v>3</v>
@@ -4631,13 +4631,13 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>0.092</v>
+        <v>0.091</v>
       </c>
       <c r="W18" t="n">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="X18" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="Y18" t="n">
         <v>-5</v>
@@ -4866,7 +4866,7 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>54545</v>
+        <v>54563</v>
       </c>
       <c r="X19" t="n">
         <v>46.2</v>
@@ -5095,10 +5095,10 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>0.671</v>
+        <v>0.673</v>
       </c>
       <c r="W20" t="n">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="X20" t="n">
         <v>10.8</v>
@@ -5330,10 +5330,10 @@
         <v>0.093</v>
       </c>
       <c r="W21" t="n">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="X21" t="n">
-        <v>40.1</v>
+        <v>40.2</v>
       </c>
       <c r="Y21" t="n">
         <v>17</v>
@@ -5553,13 +5553,13 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>1.033</v>
+        <v>1.044</v>
       </c>
       <c r="W22" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="X22" t="n">
-        <v>5.63</v>
+        <v>5.56</v>
       </c>
       <c r="Y22" t="n">
         <v>31</v>
@@ -5781,13 +5781,13 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>0.309</v>
+        <v>0.325</v>
       </c>
       <c r="W23" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="X23" t="n">
-        <v>24.9</v>
+        <v>23.6</v>
       </c>
       <c r="Y23" t="n">
         <v>12</v>
@@ -6013,13 +6013,13 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>0.376</v>
+        <v>0.375</v>
       </c>
       <c r="W24" t="n">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="X24" t="n">
-        <v>53.2</v>
+        <v>53.4</v>
       </c>
       <c r="Y24" t="n">
         <v>21</v>
@@ -6245,13 +6245,13 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>0.524</v>
+        <v>0.52</v>
       </c>
       <c r="W25" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="X25" t="n">
-        <v>35.4</v>
+        <v>35.6</v>
       </c>
       <c r="Y25" t="n">
         <v>21</v>
@@ -6477,13 +6477,13 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>0.529</v>
+        <v>0.534</v>
       </c>
       <c r="W26" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="X26" t="n">
-        <v>35.2</v>
+        <v>34.8</v>
       </c>
       <c r="Y26" t="n">
         <v>-44</v>
@@ -6709,10 +6709,10 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>0.132</v>
+        <v>0.131</v>
       </c>
       <c r="W27" t="n">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="X27" t="n">
         <v>13.4</v>
@@ -6944,7 +6944,7 @@
         <v>0.042</v>
       </c>
       <c r="W28" t="n">
-        <v>1640</v>
+        <v>1637</v>
       </c>
       <c r="X28" t="n">
         <v>21.4</v>
@@ -7173,13 +7173,13 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>0.275</v>
+        <v>0.274</v>
       </c>
       <c r="W29" t="n">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="X29" t="n">
-        <v>25.8</v>
+        <v>25.9</v>
       </c>
       <c r="Y29" t="n">
         <v>9</v>
@@ -7405,10 +7405,10 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>1.86</v>
+        <v>1.893</v>
       </c>
       <c r="W30" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="n">
@@ -7861,13 +7861,13 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>0.656</v>
+        <v>0.669</v>
       </c>
       <c r="W32" t="n">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="X32" t="n">
-        <v>1156</v>
+        <v>1131</v>
       </c>
       <c r="Y32" t="n">
         <v>-61</v>
@@ -8089,13 +8089,13 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>0.245</v>
+        <v>0.246</v>
       </c>
       <c r="W33" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="X33" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="Y33" t="n">
         <v>16</v>
@@ -8324,7 +8324,7 @@
         <v>0.234</v>
       </c>
       <c r="W34" t="n">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="X34" t="n">
         <v>18.1</v>
@@ -8556,7 +8556,7 @@
         <v>0.042</v>
       </c>
       <c r="W35" t="n">
-        <v>3178</v>
+        <v>3176</v>
       </c>
       <c r="X35" t="n">
         <v>18.8</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>0.376</v>
+        <v>0.374</v>
       </c>
       <c r="W36" t="n">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="X36" t="n">
-        <v>92.09999999999999</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="Y36" t="n">
         <v>246</v>
@@ -9020,10 +9020,10 @@
         <v>0.869</v>
       </c>
       <c r="W37" t="n">
-        <v>3638</v>
+        <v>3636</v>
       </c>
       <c r="X37" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="Y37" t="n">
         <v>2</v>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>5237</v>
+        <v>5239</v>
       </c>
       <c r="X38" t="n">
         <v>12.3</v>
@@ -9484,7 +9484,7 @@
         <v>0.011</v>
       </c>
       <c r="W39" t="n">
-        <v>4078</v>
+        <v>4068</v>
       </c>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="n">
@@ -9711,13 +9711,13 @@
         </is>
       </c>
       <c r="V40" t="n">
-        <v>0.109</v>
+        <v>0.11</v>
       </c>
       <c r="W40" t="n">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="X40" t="n">
-        <v>7.34</v>
+        <v>7.28</v>
       </c>
       <c r="Y40" t="n">
         <v>118</v>
@@ -10171,13 +10171,13 @@
         </is>
       </c>
       <c r="V42" t="n">
-        <v>0.08</v>
+        <v>0.079</v>
       </c>
       <c r="W42" t="n">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="X42" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="Y42" t="n">
         <v>-8</v>
@@ -10403,10 +10403,10 @@
         </is>
       </c>
       <c r="V43" t="n">
-        <v>0.104</v>
+        <v>0.105</v>
       </c>
       <c r="W43" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="X43" t="n">
         <v>26.2</v>
@@ -10635,10 +10635,10 @@
         </is>
       </c>
       <c r="V44" t="n">
-        <v>0.053</v>
+        <v>0.052</v>
       </c>
       <c r="W44" t="n">
-        <v>932</v>
+        <v>942</v>
       </c>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="n">
@@ -10868,7 +10868,7 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>3737</v>
+        <v>3735</v>
       </c>
       <c r="X45" t="n">
         <v>84.09999999999999</v>
@@ -11100,7 +11100,7 @@
         <v>0.006</v>
       </c>
       <c r="W46" t="n">
-        <v>4776</v>
+        <v>4771</v>
       </c>
       <c r="X46" t="n">
         <v>12.3</v>
@@ -11328,7 +11328,7 @@
         <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>103165</v>
+        <v>103029</v>
       </c>
       <c r="X47" t="n">
         <v>29.7</v>
@@ -11557,10 +11557,10 @@
         </is>
       </c>
       <c r="V48" t="n">
-        <v>0.227</v>
+        <v>0.225</v>
       </c>
       <c r="W48" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="X48" t="n">
         <v>23.6</v>

--- a/output/2026-10-09/enriched_analysis.xlsx
+++ b/output/2026-10-09/enriched_analysis.xlsx
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>2.233</v>
+        <v>2.255</v>
       </c>
       <c r="W2" t="n">
-        <v>2821</v>
+        <v>2794</v>
       </c>
       <c r="X2" t="n">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="Y2" t="n">
         <v>75</v>
@@ -1161,13 +1161,13 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>0.879</v>
+        <v>0.881</v>
       </c>
       <c r="W3" t="n">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="X3" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y3" t="n">
         <v>47</v>
@@ -1396,10 +1396,10 @@
         <v>0.046</v>
       </c>
       <c r="W4" t="n">
-        <v>2902</v>
+        <v>2899</v>
       </c>
       <c r="X4" t="n">
-        <v>9.970000000000001</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="Y4" t="n">
         <v>36</v>
@@ -1625,10 +1625,10 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>1.86</v>
+        <v>1.915</v>
       </c>
       <c r="W5" t="n">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
@@ -1855,13 +1855,13 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>0.334</v>
+        <v>0.338</v>
       </c>
       <c r="W6" t="n">
-        <v>918</v>
+        <v>907</v>
       </c>
       <c r="X6" t="n">
-        <v>9.029999999999999</v>
+        <v>8.93</v>
       </c>
       <c r="Y6" t="n">
         <v>7</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>0.136</v>
+        <v>0.129</v>
       </c>
       <c r="W7" t="n">
-        <v>2300</v>
+        <v>2430</v>
       </c>
       <c r="X7" t="n">
-        <v>20.2</v>
+        <v>21.3</v>
       </c>
       <c r="Y7" t="n">
         <v>-3</v>
@@ -2319,13 +2319,13 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>1.173</v>
+        <v>1.209</v>
       </c>
       <c r="W8" t="n">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="X8" t="n">
-        <v>7.28</v>
+        <v>7.04</v>
       </c>
       <c r="Y8" t="n">
         <v>17</v>
@@ -2557,7 +2557,7 @@
         <v>316</v>
       </c>
       <c r="X9" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Y9" t="n">
         <v>22</v>
@@ -2786,10 +2786,10 @@
         <v>0.048</v>
       </c>
       <c r="W10" t="n">
-        <v>14952</v>
+        <v>15166</v>
       </c>
       <c r="X10" t="n">
-        <v>38.1</v>
+        <v>38.6</v>
       </c>
       <c r="Y10" t="n">
         <v>83</v>
@@ -3015,13 +3015,13 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>2.348</v>
+        <v>2.356</v>
       </c>
       <c r="W11" t="n">
-        <v>2500</v>
+        <v>2491</v>
       </c>
       <c r="X11" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Y11" t="n">
         <v>6</v>
@@ -3250,10 +3250,10 @@
         <v>0.067</v>
       </c>
       <c r="W12" t="n">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="X12" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="Y12" t="n">
         <v>19</v>
@@ -3477,13 +3477,13 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>0.051</v>
+        <v>0.052</v>
       </c>
       <c r="W13" t="n">
-        <v>1602</v>
+        <v>1594</v>
       </c>
       <c r="X13" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="Y13" t="n">
         <v>55</v>
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>2561</v>
+        <v>2565</v>
       </c>
       <c r="X14" t="n">
         <v>21</v>
@@ -3941,13 +3941,13 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.066</v>
       </c>
       <c r="W15" t="n">
-        <v>1598</v>
+        <v>1685</v>
       </c>
       <c r="X15" t="n">
-        <v>36.7</v>
+        <v>38.7</v>
       </c>
       <c r="Y15" t="n">
         <v>20</v>
@@ -4179,7 +4179,7 @@
         <v>667</v>
       </c>
       <c r="X16" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="Y16" t="n">
         <v>30</v>
@@ -4399,13 +4399,13 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>0.188</v>
+        <v>0.187</v>
       </c>
       <c r="W17" t="n">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="X17" t="n">
-        <v>49.3</v>
+        <v>49.6</v>
       </c>
       <c r="Y17" t="n">
         <v>3</v>
@@ -4631,13 +4631,13 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>0.091</v>
+        <v>0.09</v>
       </c>
       <c r="W18" t="n">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="X18" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="Y18" t="n">
         <v>-5</v>
@@ -4866,10 +4866,10 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>54563</v>
+        <v>54394</v>
       </c>
       <c r="X19" t="n">
-        <v>46.2</v>
+        <v>46.1</v>
       </c>
       <c r="Y19" t="n">
         <v>5</v>
@@ -5095,13 +5095,13 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>0.673</v>
+        <v>0.608</v>
       </c>
       <c r="W20" t="n">
-        <v>431</v>
+        <v>477</v>
       </c>
       <c r="X20" t="n">
-        <v>10.8</v>
+        <v>11.9</v>
       </c>
       <c r="Y20" t="n">
         <v>19</v>
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>0.093</v>
+        <v>0.099</v>
       </c>
       <c r="W21" t="n">
-        <v>923</v>
+        <v>865</v>
       </c>
       <c r="X21" t="n">
-        <v>40.2</v>
+        <v>37.7</v>
       </c>
       <c r="Y21" t="n">
         <v>17</v>
@@ -5553,13 +5553,13 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>1.044</v>
+        <v>1.096</v>
       </c>
       <c r="W22" t="n">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="X22" t="n">
-        <v>5.56</v>
+        <v>5.28</v>
       </c>
       <c r="Y22" t="n">
         <v>31</v>
@@ -5781,13 +5781,13 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>0.325</v>
+        <v>0.328</v>
       </c>
       <c r="W23" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="X23" t="n">
-        <v>23.6</v>
+        <v>23.3</v>
       </c>
       <c r="Y23" t="n">
         <v>12</v>
@@ -6013,13 +6013,13 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>0.375</v>
+        <v>0.385</v>
       </c>
       <c r="W24" t="n">
-        <v>1048</v>
+        <v>1021</v>
       </c>
       <c r="X24" t="n">
-        <v>53.4</v>
+        <v>52</v>
       </c>
       <c r="Y24" t="n">
         <v>21</v>
@@ -6477,13 +6477,13 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>0.534</v>
+        <v>0.529</v>
       </c>
       <c r="W26" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="X26" t="n">
-        <v>34.8</v>
+        <v>35.2</v>
       </c>
       <c r="Y26" t="n">
         <v>-44</v>
@@ -6709,10 +6709,10 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>0.131</v>
+        <v>0.132</v>
       </c>
       <c r="W27" t="n">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="X27" t="n">
         <v>13.4</v>
@@ -6941,13 +6941,13 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>0.042</v>
+        <v>0.041</v>
       </c>
       <c r="W28" t="n">
-        <v>1637</v>
+        <v>1680</v>
       </c>
       <c r="X28" t="n">
-        <v>21.4</v>
+        <v>21.9</v>
       </c>
       <c r="Y28" t="n">
         <v>10</v>
@@ -7173,13 +7173,13 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>0.274</v>
+        <v>0.265</v>
       </c>
       <c r="W29" t="n">
-        <v>951</v>
+        <v>981</v>
       </c>
       <c r="X29" t="n">
-        <v>25.9</v>
+        <v>26.7</v>
       </c>
       <c r="Y29" t="n">
         <v>9</v>
@@ -7405,10 +7405,10 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>1.893</v>
+        <v>1.926</v>
       </c>
       <c r="W30" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="n">
@@ -7861,13 +7861,13 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>0.669</v>
+        <v>0.677</v>
       </c>
       <c r="W32" t="n">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="X32" t="n">
-        <v>1131</v>
+        <v>1120</v>
       </c>
       <c r="Y32" t="n">
         <v>-61</v>
@@ -8026,7 +8026,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F33" t="n">
         <v>4</v>
@@ -8089,13 +8089,13 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>0.246</v>
+        <v>0.252</v>
       </c>
       <c r="W33" t="n">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="X33" t="n">
-        <v>13.9</v>
+        <v>13.6</v>
       </c>
       <c r="Y33" t="n">
         <v>16</v>
@@ -8321,13 +8321,13 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>0.234</v>
+        <v>0.235</v>
       </c>
       <c r="W34" t="n">
-        <v>1709</v>
+        <v>1700</v>
       </c>
       <c r="X34" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="Y34" t="n">
         <v>-3</v>
@@ -8553,13 +8553,13 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>0.042</v>
+        <v>0.043</v>
       </c>
       <c r="W35" t="n">
-        <v>3176</v>
+        <v>3130</v>
       </c>
       <c r="X35" t="n">
-        <v>18.8</v>
+        <v>18.5</v>
       </c>
       <c r="Y35" t="n">
         <v>-4</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>0.374</v>
+        <v>0.376</v>
       </c>
       <c r="W36" t="n">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="X36" t="n">
-        <v>92.59999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="Y36" t="n">
         <v>246</v>
@@ -9017,13 +9017,13 @@
         </is>
       </c>
       <c r="V37" t="n">
-        <v>0.869</v>
+        <v>0.874</v>
       </c>
       <c r="W37" t="n">
-        <v>3636</v>
+        <v>3614</v>
       </c>
       <c r="X37" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="Y37" t="n">
         <v>2</v>
@@ -9252,10 +9252,10 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>5239</v>
+        <v>5271</v>
       </c>
       <c r="X38" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="Y38" t="n">
         <v>26</v>
@@ -9484,7 +9484,7 @@
         <v>0.011</v>
       </c>
       <c r="W39" t="n">
-        <v>4068</v>
+        <v>4056</v>
       </c>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="n">
@@ -9711,13 +9711,13 @@
         </is>
       </c>
       <c r="V40" t="n">
-        <v>0.11</v>
+        <v>0.105</v>
       </c>
       <c r="W40" t="n">
-        <v>451</v>
+        <v>473</v>
       </c>
       <c r="X40" t="n">
-        <v>7.28</v>
+        <v>7.62</v>
       </c>
       <c r="Y40" t="n">
         <v>118</v>
@@ -9939,13 +9939,13 @@
         </is>
       </c>
       <c r="V41" t="n">
-        <v>0.132</v>
+        <v>0.138</v>
       </c>
       <c r="W41" t="n">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="X41" t="n">
-        <v>35.4</v>
+        <v>33.7</v>
       </c>
       <c r="Y41" t="n">
         <v>19</v>
@@ -10174,10 +10174,10 @@
         <v>0.079</v>
       </c>
       <c r="W42" t="n">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="X42" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="Y42" t="n">
         <v>-8</v>
@@ -10403,13 +10403,13 @@
         </is>
       </c>
       <c r="V43" t="n">
-        <v>0.105</v>
+        <v>0.102</v>
       </c>
       <c r="W43" t="n">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="X43" t="n">
-        <v>26.2</v>
+        <v>27</v>
       </c>
       <c r="Y43" t="n">
         <v>24</v>
@@ -10638,7 +10638,7 @@
         <v>0.052</v>
       </c>
       <c r="W44" t="n">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="n">
@@ -10868,10 +10868,10 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>3735</v>
+        <v>3584</v>
       </c>
       <c r="X45" t="n">
-        <v>84.09999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="Y45" t="n">
         <v>42</v>
@@ -11100,10 +11100,10 @@
         <v>0.006</v>
       </c>
       <c r="W46" t="n">
-        <v>4771</v>
+        <v>4835</v>
       </c>
       <c r="X46" t="n">
-        <v>12.3</v>
+        <v>12.5</v>
       </c>
       <c r="Y46" t="n">
         <v>23</v>
@@ -11328,10 +11328,10 @@
         <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>103029</v>
+        <v>103366</v>
       </c>
       <c r="X47" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="Y47" t="n">
         <v>18</v>
@@ -11557,13 +11557,13 @@
         </is>
       </c>
       <c r="V48" t="n">
-        <v>0.225</v>
+        <v>0.229</v>
       </c>
       <c r="W48" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="X48" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="Y48" t="n">
         <v>21</v>

--- a/output/2026-10-09/enriched_analysis.xlsx
+++ b/output/2026-10-09/enriched_analysis.xlsx
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>2.255</v>
+        <v>2.25</v>
       </c>
       <c r="W2" t="n">
-        <v>2794</v>
+        <v>2800</v>
       </c>
       <c r="X2" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="Y2" t="n">
         <v>75</v>
@@ -1396,10 +1396,10 @@
         <v>0.046</v>
       </c>
       <c r="W4" t="n">
-        <v>2899</v>
+        <v>2909</v>
       </c>
       <c r="X4" t="n">
-        <v>9.960000000000001</v>
+        <v>9.99</v>
       </c>
       <c r="Y4" t="n">
         <v>36</v>
@@ -1625,10 +1625,10 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>1.915</v>
+        <v>1.86</v>
       </c>
       <c r="W5" t="n">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>0.129</v>
+        <v>0.131</v>
       </c>
       <c r="W7" t="n">
-        <v>2430</v>
+        <v>2393</v>
       </c>
       <c r="X7" t="n">
-        <v>21.3</v>
+        <v>21</v>
       </c>
       <c r="Y7" t="n">
         <v>-3</v>
@@ -2319,13 +2319,13 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>1.209</v>
+        <v>1.202</v>
       </c>
       <c r="W8" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="X8" t="n">
-        <v>7.04</v>
+        <v>7.09</v>
       </c>
       <c r="Y8" t="n">
         <v>17</v>
@@ -2783,13 +2783,13 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>0.048</v>
+        <v>0.047</v>
       </c>
       <c r="W10" t="n">
-        <v>15166</v>
+        <v>15177</v>
       </c>
       <c r="X10" t="n">
-        <v>38.6</v>
+        <v>38.7</v>
       </c>
       <c r="Y10" t="n">
         <v>83</v>
@@ -3250,7 +3250,7 @@
         <v>0.067</v>
       </c>
       <c r="W12" t="n">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="X12" t="n">
         <v>21.4</v>
@@ -3477,13 +3477,13 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>0.052</v>
+        <v>0.051</v>
       </c>
       <c r="W13" t="n">
-        <v>1594</v>
+        <v>1604</v>
       </c>
       <c r="X13" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="Y13" t="n">
         <v>55</v>
@@ -3944,10 +3944,10 @@
         <v>0.066</v>
       </c>
       <c r="W15" t="n">
-        <v>1685</v>
+        <v>1679</v>
       </c>
       <c r="X15" t="n">
-        <v>38.7</v>
+        <v>38.5</v>
       </c>
       <c r="Y15" t="n">
         <v>20</v>
@@ -4173,13 +4173,13 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>2.95</v>
+        <v>2.964</v>
       </c>
       <c r="W16" t="n">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="X16" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="Y16" t="n">
         <v>30</v>
@@ -4399,13 +4399,13 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>0.187</v>
+        <v>0.191</v>
       </c>
       <c r="W17" t="n">
-        <v>594</v>
+        <v>581</v>
       </c>
       <c r="X17" t="n">
-        <v>49.6</v>
+        <v>48.5</v>
       </c>
       <c r="Y17" t="n">
         <v>3</v>
@@ -4866,7 +4866,7 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>54394</v>
+        <v>54446</v>
       </c>
       <c r="X19" t="n">
         <v>46.1</v>
@@ -5330,10 +5330,10 @@
         <v>0.099</v>
       </c>
       <c r="W21" t="n">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="X21" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="Y21" t="n">
         <v>17</v>
@@ -5781,13 +5781,13 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>0.328</v>
+        <v>0.33</v>
       </c>
       <c r="W23" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="X23" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="Y23" t="n">
         <v>12</v>
@@ -6013,13 +6013,13 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>0.385</v>
+        <v>0.384</v>
       </c>
       <c r="W24" t="n">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="X24" t="n">
-        <v>52</v>
+        <v>52.2</v>
       </c>
       <c r="Y24" t="n">
         <v>21</v>
@@ -6477,13 +6477,13 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>0.529</v>
+        <v>0.532</v>
       </c>
       <c r="W26" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="X26" t="n">
-        <v>35.2</v>
+        <v>35</v>
       </c>
       <c r="Y26" t="n">
         <v>-44</v>
@@ -6712,7 +6712,7 @@
         <v>0.132</v>
       </c>
       <c r="W27" t="n">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="X27" t="n">
         <v>13.4</v>
@@ -6944,7 +6944,7 @@
         <v>0.041</v>
       </c>
       <c r="W28" t="n">
-        <v>1680</v>
+        <v>1678</v>
       </c>
       <c r="X28" t="n">
         <v>21.9</v>
@@ -7173,13 +7173,13 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>0.265</v>
+        <v>0.267</v>
       </c>
       <c r="W29" t="n">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="X29" t="n">
-        <v>26.7</v>
+        <v>26.5</v>
       </c>
       <c r="Y29" t="n">
         <v>9</v>
@@ -7405,10 +7405,10 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>1.926</v>
+        <v>1.909</v>
       </c>
       <c r="W30" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="n">
@@ -8089,13 +8089,13 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>0.252</v>
+        <v>0.259</v>
       </c>
       <c r="W33" t="n">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="X33" t="n">
-        <v>13.6</v>
+        <v>13.2</v>
       </c>
       <c r="Y33" t="n">
         <v>16</v>
@@ -8556,10 +8556,10 @@
         <v>0.043</v>
       </c>
       <c r="W35" t="n">
-        <v>3130</v>
+        <v>3153</v>
       </c>
       <c r="X35" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="Y35" t="n">
         <v>-4</v>
@@ -9017,13 +9017,13 @@
         </is>
       </c>
       <c r="V37" t="n">
-        <v>0.874</v>
+        <v>0.879</v>
       </c>
       <c r="W37" t="n">
-        <v>3614</v>
+        <v>3596</v>
       </c>
       <c r="X37" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="Y37" t="n">
         <v>2</v>
@@ -9252,10 +9252,10 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>5271</v>
+        <v>5209</v>
       </c>
       <c r="X38" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="Y38" t="n">
         <v>26</v>
@@ -9484,7 +9484,7 @@
         <v>0.011</v>
       </c>
       <c r="W39" t="n">
-        <v>4056</v>
+        <v>4065</v>
       </c>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="n">
@@ -9711,13 +9711,13 @@
         </is>
       </c>
       <c r="V40" t="n">
-        <v>0.105</v>
+        <v>0.106</v>
       </c>
       <c r="W40" t="n">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="X40" t="n">
-        <v>7.62</v>
+        <v>7.5</v>
       </c>
       <c r="Y40" t="n">
         <v>118</v>
@@ -10340,7 +10340,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
         <v>8</v>
@@ -10403,13 +10403,13 @@
         </is>
       </c>
       <c r="V43" t="n">
-        <v>0.102</v>
+        <v>0.097</v>
       </c>
       <c r="W43" t="n">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="X43" t="n">
-        <v>27</v>
+        <v>28.3</v>
       </c>
       <c r="Y43" t="n">
         <v>24</v>
@@ -10635,10 +10635,10 @@
         </is>
       </c>
       <c r="V44" t="n">
-        <v>0.052</v>
+        <v>0.051</v>
       </c>
       <c r="W44" t="n">
-        <v>943</v>
+        <v>959</v>
       </c>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="n">
@@ -10868,10 +10868,10 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>3584</v>
+        <v>3575</v>
       </c>
       <c r="X45" t="n">
-        <v>80.7</v>
+        <v>80.5</v>
       </c>
       <c r="Y45" t="n">
         <v>42</v>
@@ -11100,7 +11100,7 @@
         <v>0.006</v>
       </c>
       <c r="W46" t="n">
-        <v>4835</v>
+        <v>4827</v>
       </c>
       <c r="X46" t="n">
         <v>12.5</v>
@@ -11328,7 +11328,7 @@
         <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>103366</v>
+        <v>103646</v>
       </c>
       <c r="X47" t="n">
         <v>29.8</v>

--- a/output/2026-10-09/enriched_analysis.xlsx
+++ b/output/2026-10-09/enriched_analysis.xlsx
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>2.25</v>
+        <v>2.257</v>
       </c>
       <c r="W2" t="n">
-        <v>2800</v>
+        <v>2791</v>
       </c>
       <c r="X2" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="Y2" t="n">
         <v>75</v>
@@ -1161,13 +1161,13 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>0.881</v>
+        <v>0.879</v>
       </c>
       <c r="W3" t="n">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="X3" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Y3" t="n">
         <v>47</v>
@@ -1393,13 +1393,13 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>0.046</v>
+        <v>0.045</v>
       </c>
       <c r="W4" t="n">
-        <v>2909</v>
+        <v>2919</v>
       </c>
       <c r="X4" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="Y4" t="n">
         <v>36</v>
@@ -1625,10 +1625,10 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>1.86</v>
+        <v>1.922</v>
       </c>
       <c r="W5" t="n">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
@@ -1855,13 +1855,13 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>0.338</v>
+        <v>0.334</v>
       </c>
       <c r="W6" t="n">
-        <v>907</v>
+        <v>918</v>
       </c>
       <c r="X6" t="n">
-        <v>8.93</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="Y6" t="n">
         <v>7</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>0.131</v>
+        <v>0.13</v>
       </c>
       <c r="W7" t="n">
-        <v>2393</v>
+        <v>2424</v>
       </c>
       <c r="X7" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="Y7" t="n">
         <v>-3</v>
@@ -2319,13 +2319,13 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>1.202</v>
+        <v>1.187</v>
       </c>
       <c r="W8" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="X8" t="n">
-        <v>7.09</v>
+        <v>7.17</v>
       </c>
       <c r="Y8" t="n">
         <v>17</v>
@@ -2557,7 +2557,7 @@
         <v>316</v>
       </c>
       <c r="X9" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Y9" t="n">
         <v>22</v>
@@ -2786,10 +2786,10 @@
         <v>0.047</v>
       </c>
       <c r="W10" t="n">
-        <v>15177</v>
+        <v>15291</v>
       </c>
       <c r="X10" t="n">
-        <v>38.7</v>
+        <v>39</v>
       </c>
       <c r="Y10" t="n">
         <v>83</v>
@@ -3015,13 +3015,13 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>2.356</v>
+        <v>2.324</v>
       </c>
       <c r="W11" t="n">
-        <v>2491</v>
+        <v>2526</v>
       </c>
       <c r="X11" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Y11" t="n">
         <v>6</v>
@@ -3247,13 +3247,13 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>0.067</v>
+        <v>0.068</v>
       </c>
       <c r="W12" t="n">
-        <v>848</v>
+        <v>831</v>
       </c>
       <c r="X12" t="n">
-        <v>21.4</v>
+        <v>21</v>
       </c>
       <c r="Y12" t="n">
         <v>19</v>
@@ -3477,13 +3477,13 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>0.051</v>
+        <v>0.052</v>
       </c>
       <c r="W13" t="n">
-        <v>1604</v>
+        <v>1597</v>
       </c>
       <c r="X13" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="Y13" t="n">
         <v>55</v>
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>2565</v>
+        <v>2557</v>
       </c>
       <c r="X14" t="n">
         <v>21</v>
@@ -3941,13 +3941,13 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>0.066</v>
+        <v>0.067</v>
       </c>
       <c r="W15" t="n">
-        <v>1679</v>
+        <v>1651</v>
       </c>
       <c r="X15" t="n">
-        <v>38.5</v>
+        <v>37.9</v>
       </c>
       <c r="Y15" t="n">
         <v>20</v>
@@ -4173,13 +4173,13 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>2.964</v>
+        <v>3.018</v>
       </c>
       <c r="W16" t="n">
-        <v>664</v>
+        <v>652</v>
       </c>
       <c r="X16" t="n">
-        <v>20</v>
+        <v>19.6</v>
       </c>
       <c r="Y16" t="n">
         <v>30</v>
@@ -4399,13 +4399,13 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>0.191</v>
+        <v>0.181</v>
       </c>
       <c r="W17" t="n">
-        <v>581</v>
+        <v>612</v>
       </c>
       <c r="X17" t="n">
-        <v>48.5</v>
+        <v>51.1</v>
       </c>
       <c r="Y17" t="n">
         <v>3</v>
@@ -4634,10 +4634,10 @@
         <v>0.09</v>
       </c>
       <c r="W18" t="n">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="X18" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="Y18" t="n">
         <v>-5</v>
@@ -4866,10 +4866,10 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>54446</v>
+        <v>55105</v>
       </c>
       <c r="X19" t="n">
-        <v>46.1</v>
+        <v>46.7</v>
       </c>
       <c r="Y19" t="n">
         <v>5</v>
@@ -5095,13 +5095,13 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>0.608</v>
+        <v>0.616</v>
       </c>
       <c r="W20" t="n">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="X20" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="Y20" t="n">
         <v>19</v>
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>0.099</v>
+        <v>0.1</v>
       </c>
       <c r="W21" t="n">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="X21" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="Y21" t="n">
         <v>17</v>
@@ -5781,13 +5781,13 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>0.33</v>
+        <v>0.335</v>
       </c>
       <c r="W23" t="n">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="X23" t="n">
-        <v>23.2</v>
+        <v>22.8</v>
       </c>
       <c r="Y23" t="n">
         <v>12</v>
@@ -6013,13 +6013,13 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>0.384</v>
+        <v>0.387</v>
       </c>
       <c r="W24" t="n">
-        <v>1024</v>
+        <v>1017</v>
       </c>
       <c r="X24" t="n">
-        <v>52.2</v>
+        <v>51.8</v>
       </c>
       <c r="Y24" t="n">
         <v>21</v>
@@ -6477,13 +6477,13 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>0.532</v>
+        <v>0.524</v>
       </c>
       <c r="W26" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="X26" t="n">
-        <v>35</v>
+        <v>35.6</v>
       </c>
       <c r="Y26" t="n">
         <v>-44</v>
@@ -6709,13 +6709,13 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>0.132</v>
+        <v>0.13</v>
       </c>
       <c r="W27" t="n">
-        <v>606</v>
+        <v>616</v>
       </c>
       <c r="X27" t="n">
-        <v>13.4</v>
+        <v>13.6</v>
       </c>
       <c r="Y27" t="n">
         <v>-1</v>
@@ -6941,13 +6941,13 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>0.041</v>
+        <v>0.042</v>
       </c>
       <c r="W28" t="n">
-        <v>1678</v>
+        <v>1650</v>
       </c>
       <c r="X28" t="n">
-        <v>21.9</v>
+        <v>21.5</v>
       </c>
       <c r="Y28" t="n">
         <v>10</v>
@@ -7173,13 +7173,13 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>0.267</v>
+        <v>0.263</v>
       </c>
       <c r="W29" t="n">
-        <v>974</v>
+        <v>989</v>
       </c>
       <c r="X29" t="n">
-        <v>26.5</v>
+        <v>26.9</v>
       </c>
       <c r="Y29" t="n">
         <v>9</v>
@@ -7867,7 +7867,7 @@
         <v>347</v>
       </c>
       <c r="X32" t="n">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="Y32" t="n">
         <v>-61</v>
@@ -8089,13 +8089,13 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>0.259</v>
+        <v>0.255</v>
       </c>
       <c r="W33" t="n">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="X33" t="n">
-        <v>13.2</v>
+        <v>13.4</v>
       </c>
       <c r="Y33" t="n">
         <v>16</v>
@@ -8321,13 +8321,13 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>0.235</v>
+        <v>0.233</v>
       </c>
       <c r="W34" t="n">
-        <v>1700</v>
+        <v>1716</v>
       </c>
       <c r="X34" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="Y34" t="n">
         <v>-3</v>
@@ -8553,13 +8553,13 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>0.043</v>
+        <v>0.042</v>
       </c>
       <c r="W35" t="n">
-        <v>3153</v>
+        <v>3168</v>
       </c>
       <c r="X35" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="Y35" t="n">
         <v>-4</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>0.376</v>
+        <v>0.367</v>
       </c>
       <c r="W36" t="n">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="X36" t="n">
-        <v>92.09999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="Y36" t="n">
         <v>246</v>
@@ -9017,13 +9017,13 @@
         </is>
       </c>
       <c r="V37" t="n">
-        <v>0.879</v>
+        <v>0.865</v>
       </c>
       <c r="W37" t="n">
-        <v>3596</v>
+        <v>3653</v>
       </c>
       <c r="X37" t="n">
-        <v>25.2</v>
+        <v>25.6</v>
       </c>
       <c r="Y37" t="n">
         <v>2</v>
@@ -9252,10 +9252,10 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>5209</v>
+        <v>5232</v>
       </c>
       <c r="X38" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="Y38" t="n">
         <v>26</v>
@@ -9484,7 +9484,7 @@
         <v>0.011</v>
       </c>
       <c r="W39" t="n">
-        <v>4065</v>
+        <v>4154</v>
       </c>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="n">
@@ -9711,13 +9711,13 @@
         </is>
       </c>
       <c r="V40" t="n">
-        <v>0.106</v>
+        <v>0.108</v>
       </c>
       <c r="W40" t="n">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="X40" t="n">
-        <v>7.5</v>
+        <v>7.38</v>
       </c>
       <c r="Y40" t="n">
         <v>118</v>
@@ -10171,13 +10171,13 @@
         </is>
       </c>
       <c r="V42" t="n">
-        <v>0.079</v>
+        <v>0.078</v>
       </c>
       <c r="W42" t="n">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="X42" t="n">
-        <v>12.6</v>
+        <v>12.8</v>
       </c>
       <c r="Y42" t="n">
         <v>-8</v>
@@ -10340,7 +10340,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F43" t="n">
         <v>8</v>
@@ -10403,13 +10403,13 @@
         </is>
       </c>
       <c r="V43" t="n">
-        <v>0.097</v>
+        <v>0.102</v>
       </c>
       <c r="W43" t="n">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="X43" t="n">
-        <v>28.3</v>
+        <v>26.8</v>
       </c>
       <c r="Y43" t="n">
         <v>24</v>
@@ -10868,10 +10868,10 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>3575</v>
+        <v>3662</v>
       </c>
       <c r="X45" t="n">
-        <v>80.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="Y45" t="n">
         <v>42</v>
@@ -11100,7 +11100,7 @@
         <v>0.006</v>
       </c>
       <c r="W46" t="n">
-        <v>4827</v>
+        <v>4840</v>
       </c>
       <c r="X46" t="n">
         <v>12.5</v>
@@ -11328,7 +11328,7 @@
         <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>103646</v>
+        <v>103529</v>
       </c>
       <c r="X47" t="n">
         <v>29.8</v>
@@ -11557,13 +11557,13 @@
         </is>
       </c>
       <c r="V48" t="n">
-        <v>0.229</v>
+        <v>0.231</v>
       </c>
       <c r="W48" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="X48" t="n">
-        <v>23.4</v>
+        <v>23.1</v>
       </c>
       <c r="Y48" t="n">
         <v>21</v>

--- a/output/2026-10-09/enriched_analysis.xlsx
+++ b/output/2026-10-09/enriched_analysis.xlsx
@@ -886,13 +886,13 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>84.90000000000001</v>
+        <v>83.67</v>
       </c>
       <c r="J2" t="n">
         <v>77.33</v>
       </c>
       <c r="K2" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L2" t="n">
         <v>61.32</v>
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>2.257</v>
+        <v>2.268</v>
       </c>
       <c r="W2" t="n">
-        <v>2791</v>
+        <v>2778</v>
       </c>
       <c r="X2" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="Y2" t="n">
         <v>75</v>
@@ -962,19 +962,19 @@
         <v>6</v>
       </c>
       <c r="AG2" t="n">
-        <v>82.13</v>
+        <v>82.23999999999999</v>
       </c>
       <c r="AH2" t="n">
-        <v>58.5</v>
+        <v>58.74</v>
       </c>
       <c r="AI2" t="n">
-        <v>41.9</v>
+        <v>55.4</v>
       </c>
       <c r="AJ2" t="n">
         <v>77.33020135925074</v>
       </c>
       <c r="AK2" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1118,13 +1118,13 @@
         <v>-1</v>
       </c>
       <c r="I3" t="n">
-        <v>801.3</v>
+        <v>795.9</v>
       </c>
       <c r="J3" t="n">
         <v>819.08</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.2</v>
+        <v>-2.8</v>
       </c>
       <c r="L3" t="n">
         <v>73</v>
@@ -1161,13 +1161,13 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>0.879</v>
+        <v>0.885</v>
       </c>
       <c r="W3" t="n">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="X3" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y3" t="n">
         <v>47</v>
@@ -1194,19 +1194,19 @@
         <v>25.79</v>
       </c>
       <c r="AG3" t="n">
-        <v>788.2</v>
+        <v>789.1900000000001</v>
       </c>
       <c r="AH3" t="n">
-        <v>670.22</v>
+        <v>670.52</v>
       </c>
       <c r="AI3" t="n">
-        <v>50.9</v>
+        <v>39.4</v>
       </c>
       <c r="AJ3" t="n">
         <v>819.0814633455414</v>
       </c>
       <c r="AK3" t="n">
-        <v>-2.2</v>
+        <v>-2.8</v>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
@@ -1350,13 +1350,13 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>296.45</v>
+        <v>296.55</v>
       </c>
       <c r="J4" t="n">
         <v>265.56</v>
       </c>
       <c r="K4" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="L4" t="n">
         <v>64.63</v>
@@ -1393,10 +1393,10 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>0.045</v>
+        <v>0.046</v>
       </c>
       <c r="W4" t="n">
-        <v>2919</v>
+        <v>2914</v>
       </c>
       <c r="X4" t="n">
         <v>10</v>
@@ -1426,19 +1426,19 @@
         <v>16</v>
       </c>
       <c r="AG4" t="n">
-        <v>258.13</v>
+        <v>259.42</v>
       </c>
       <c r="AH4" t="n">
-        <v>182.45</v>
+        <v>183.24</v>
       </c>
       <c r="AI4" t="n">
-        <v>133.7</v>
+        <v>120.4</v>
       </c>
       <c r="AJ4" t="n">
         <v>265.56012</v>
       </c>
       <c r="AK4" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
@@ -1582,13 +1582,13 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>899.9</v>
+        <v>899</v>
       </c>
       <c r="J5" t="n">
         <v>869.9299999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L5" t="n">
         <v>61.71</v>
@@ -1625,10 +1625,10 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>1.922</v>
+        <v>1.867</v>
       </c>
       <c r="W5" t="n">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
@@ -1656,19 +1656,19 @@
         <v>57.93</v>
       </c>
       <c r="AG5" t="n">
-        <v>842.6900000000001</v>
+        <v>846.5700000000001</v>
       </c>
       <c r="AH5" t="n">
-        <v>793.12</v>
+        <v>793.78</v>
       </c>
       <c r="AI5" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="AJ5" t="n">
         <v>869.9263759469062</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
@@ -1812,13 +1812,13 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>534.75</v>
+        <v>533.85</v>
       </c>
       <c r="J6" t="n">
         <v>510.94</v>
       </c>
       <c r="K6" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L6" t="n">
         <v>62.09</v>
@@ -1855,13 +1855,13 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>0.334</v>
+        <v>0.335</v>
       </c>
       <c r="W6" t="n">
-        <v>918</v>
+        <v>913</v>
       </c>
       <c r="X6" t="n">
-        <v>9.050000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="Y6" t="n">
         <v>7</v>
@@ -1888,19 +1888,19 @@
         <v>14</v>
       </c>
       <c r="AG6" t="n">
-        <v>517.33</v>
+        <v>518.38</v>
       </c>
       <c r="AH6" t="n">
-        <v>492.38</v>
+        <v>492.39</v>
       </c>
       <c r="AI6" t="n">
-        <v>22.3</v>
+        <v>18.8</v>
       </c>
       <c r="AJ6" t="n">
         <v>510.9380308010612</v>
       </c>
       <c r="AK6" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
@@ -2015,12 +2015,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>INDORAMA</t>
+          <t>SIGIND</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>INDO RAMA SYNTHETICS (INDIA) LIMITED</t>
+          <t>Signet Industries Limited</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -2032,40 +2032,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F7" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G7" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>88.09999999999999</v>
+        <v>61.05</v>
       </c>
       <c r="J7" t="n">
-        <v>75.68000000000001</v>
+        <v>74.22</v>
       </c>
       <c r="K7" t="n">
-        <v>16.4</v>
+        <v>-17.7</v>
       </c>
       <c r="L7" t="n">
-        <v>74.84999999999999</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>3.14</v>
+        <v>2.01</v>
       </c>
       <c r="N7" t="n">
-        <v>31393588</v>
+        <v>20066329</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>31393588</v>
+        <v>20066329</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -2079,60 +2079,60 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>0.13</v>
+        <v>1.115</v>
       </c>
       <c r="W7" t="n">
-        <v>2424</v>
+        <v>180</v>
       </c>
       <c r="X7" t="n">
-        <v>21.2</v>
+        <v>7.67</v>
       </c>
       <c r="Y7" t="n">
-        <v>-3</v>
+        <v>17</v>
       </c>
       <c r="Z7" t="n">
-        <v>62</v>
+        <v>27.97</v>
       </c>
       <c r="AA7" t="n">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.29</v>
+        <v>2.73</v>
       </c>
       <c r="AC7" t="n">
-        <v>15.8</v>
+        <v>13.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="AE7" t="b">
         <v>1</v>
       </c>
       <c r="AF7" t="n">
-        <v>8</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AG7" t="n">
-        <v>74.89</v>
+        <v>67.55</v>
       </c>
       <c r="AH7" t="n">
-        <v>49.64</v>
+        <v>53.42</v>
       </c>
       <c r="AI7" t="n">
-        <v>159.6</v>
+        <v>25.6</v>
       </c>
       <c r="AJ7" t="n">
-        <v>75.6844038997483</v>
+        <v>74.21830535305453</v>
       </c>
       <c r="AK7" t="n">
-        <v>16.4</v>
+        <v>-17.7</v>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
@@ -2141,32 +2141,32 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>Mature — Wait for Pullback</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>08-09-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="AR7" t="n">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="AS7" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="AT7" t="n">
         <v>0</v>
@@ -2175,13 +2175,13 @@
         <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AW7" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="AX7" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="AY7" t="n">
         <v>0</v>
@@ -2190,13 +2190,13 @@
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>4495075</v>
       </c>
       <c r="BB7" t="n">
-        <v>31393588</v>
+        <v>20066329</v>
       </c>
       <c r="BC7" t="n">
-        <v>31393588</v>
+        <v>20066329</v>
       </c>
       <c r="BD7" t="n">
         <v>0</v>
@@ -2232,7 +2232,7 @@
         <v>0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>4495075</v>
       </c>
       <c r="BP7" t="n">
         <v>1</v>
@@ -2247,16 +2247,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SIGIND</t>
+          <t>NURECA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Signet Industries Limited</t>
+          <t>NURECA LIMITED</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2264,40 +2264,40 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F8" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
         <v>13</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I8" t="n">
-        <v>58.16</v>
+        <v>331.65</v>
       </c>
       <c r="J8" t="n">
-        <v>74.22</v>
+        <v>333.11</v>
       </c>
       <c r="K8" t="n">
-        <v>-21.6</v>
+        <v>-0.4</v>
       </c>
       <c r="L8" t="n">
-        <v>72.56999999999999</v>
+        <v>63.24</v>
       </c>
       <c r="M8" t="n">
-        <v>2.01</v>
+        <v>3.75</v>
       </c>
       <c r="N8" t="n">
-        <v>20066329</v>
+        <v>37538354</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>20066329</v>
+        <v>37538354</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2311,60 +2311,60 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>1.187</v>
+        <v>1.184</v>
       </c>
       <c r="W8" t="n">
-        <v>169</v>
+        <v>317</v>
       </c>
       <c r="X8" t="n">
-        <v>7.17</v>
+        <v>146</v>
       </c>
       <c r="Y8" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="Z8" t="n">
-        <v>27.97</v>
+        <v>2.45</v>
       </c>
       <c r="AA8" t="n">
-        <v>17</v>
+        <v>264</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.73</v>
+        <v>2.55</v>
       </c>
       <c r="AC8" t="n">
-        <v>13.6</v>
+        <v>2.07</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.86</v>
+        <v>0.01</v>
       </c>
       <c r="AE8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>9.140000000000001</v>
+        <v>6.06</v>
       </c>
       <c r="AG8" t="n">
-        <v>67.31</v>
+        <v>333.49</v>
       </c>
       <c r="AH8" t="n">
-        <v>53.4</v>
+        <v>284.39</v>
       </c>
       <c r="AI8" t="n">
-        <v>26.6</v>
+        <v>29.9</v>
       </c>
       <c r="AJ8" t="n">
-        <v>74.21830535305453</v>
+        <v>333.1146252074293</v>
       </c>
       <c r="AK8" t="n">
-        <v>-21.6</v>
+        <v>-0.4</v>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
@@ -2383,52 +2383,52 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>24-07-2026</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="AR8" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="AS8" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV8" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AW8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX8" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="AY8" t="n">
         <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>9274743</v>
       </c>
       <c r="BA8" t="n">
-        <v>4495075</v>
+        <v>19489666</v>
       </c>
       <c r="BB8" t="n">
-        <v>20066329</v>
+        <v>23414636</v>
       </c>
       <c r="BC8" t="n">
-        <v>20066329</v>
+        <v>37538354</v>
       </c>
       <c r="BD8" t="n">
         <v>0</v>
@@ -2464,10 +2464,10 @@
         <v>0</v>
       </c>
       <c r="BO8" t="n">
-        <v>4495075</v>
+        <v>19489666</v>
       </c>
       <c r="BP8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BQ8" t="n">
         <v>0</v>
@@ -2479,16 +2479,16 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NURECA</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NURECA LIMITED</t>
+          <t>THANGAMAYIL JEWELLERY LIMITED</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2496,40 +2496,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="G9" t="n">
         <v>13</v>
       </c>
       <c r="H9" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>331.35</v>
+        <v>4889.5</v>
       </c>
       <c r="J9" t="n">
-        <v>333.11</v>
+        <v>5198.76</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5</v>
+        <v>-5.9</v>
       </c>
       <c r="L9" t="n">
-        <v>63.24</v>
+        <v>67.16</v>
       </c>
       <c r="M9" t="n">
-        <v>3.75</v>
+        <v>7.21</v>
       </c>
       <c r="N9" t="n">
-        <v>37538354</v>
+        <v>72054758</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>37538354</v>
+        <v>72054758</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2543,124 +2543,124 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>1.188</v>
+        <v>0.047</v>
       </c>
       <c r="W9" t="n">
-        <v>316</v>
+        <v>15190</v>
       </c>
       <c r="X9" t="n">
-        <v>146</v>
+        <v>38.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.45</v>
+        <v>145</v>
       </c>
       <c r="AA9" t="n">
         <v>264</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.55</v>
+        <v>27.38</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.07</v>
+        <v>25.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.01</v>
+        <v>0.64</v>
       </c>
       <c r="AE9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF9" t="n">
-        <v>6.06</v>
+        <v>5</v>
       </c>
       <c r="AG9" t="n">
-        <v>333.39</v>
+        <v>5189.82</v>
       </c>
       <c r="AH9" t="n">
-        <v>284.11</v>
+        <v>4532.93</v>
       </c>
       <c r="AI9" t="n">
-        <v>38.9</v>
+        <v>21.1</v>
       </c>
       <c r="AJ9" t="n">
-        <v>333.1146252074293</v>
+        <v>5198.755988455989</v>
       </c>
       <c r="AK9" t="n">
-        <v>-0.5</v>
+        <v>-5.9</v>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>24-07-2026</t>
+          <t>04-08-2026</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="AR9" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="AS9" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="AX9" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="AY9" t="n">
         <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>9274743</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>19489666</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>23414636</v>
+        <v>19879002</v>
       </c>
       <c r="BC9" t="n">
-        <v>37538354</v>
+        <v>72054758</v>
       </c>
       <c r="BD9" t="n">
         <v>0</v>
@@ -2696,7 +2696,7 @@
         <v>0</v>
       </c>
       <c r="BO9" t="n">
-        <v>19489666</v>
+        <v>0</v>
       </c>
       <c r="BP9" t="n">
         <v>3</v>
@@ -2711,12 +2711,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>BMWVENTLTD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>THANGAMAYIL JEWELLERY LIMITED</t>
+          <t>BMW VENTURES LIMITED</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -2728,40 +2728,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F10" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G10" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I10" t="n">
-        <v>4810.5</v>
+        <v>57.95</v>
       </c>
       <c r="J10" t="n">
-        <v>5198.76</v>
+        <v>55.06</v>
       </c>
       <c r="K10" t="n">
-        <v>-7.5</v>
+        <v>5.2</v>
       </c>
       <c r="L10" t="n">
-        <v>67.16</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>7.21</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>72054758</v>
+        <v>28991535</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>72054758</v>
+        <v>28991535</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2779,90 +2779,90 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>22-09-2026</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>0.047</v>
+        <v>0.578</v>
       </c>
       <c r="W10" t="n">
-        <v>15291</v>
+        <v>502</v>
       </c>
       <c r="X10" t="n">
-        <v>39</v>
+        <v>12.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>83</v>
+        <v>19</v>
       </c>
       <c r="Z10" t="n">
-        <v>145</v>
+        <v>21</v>
       </c>
       <c r="AA10" t="n">
-        <v>264</v>
+        <v>20</v>
       </c>
       <c r="AB10" t="n">
-        <v>27.38</v>
+        <v>1.22</v>
       </c>
       <c r="AC10" t="n">
-        <v>25.5</v>
+        <v>12</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AE10" t="b">
         <v>1</v>
       </c>
       <c r="AF10" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="AG10" t="n">
-        <v>5221.07</v>
+        <v>54.97</v>
       </c>
       <c r="AH10" t="n">
-        <v>4524.55</v>
+        <v>57.62</v>
       </c>
       <c r="AI10" t="n">
-        <v>24.5</v>
+        <v>-0.7</v>
       </c>
       <c r="AJ10" t="n">
-        <v>5198.755988455989</v>
+        <v>55.06464387464388</v>
       </c>
       <c r="AK10" t="n">
-        <v>-7.5</v>
+        <v>5.2</v>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>Aging</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>Mature — Wait for Pullback</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>04-08-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>22-09-2026</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="AR10" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AS10" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="AT10" t="n">
         <v>0</v>
@@ -2871,10 +2871,10 @@
         <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AX10" t="n">
         <v>6</v>
@@ -2886,13 +2886,13 @@
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>10009832</v>
       </c>
       <c r="BB10" t="n">
-        <v>19879002</v>
+        <v>19968394</v>
       </c>
       <c r="BC10" t="n">
-        <v>72054758</v>
+        <v>28991535</v>
       </c>
       <c r="BD10" t="n">
         <v>0</v>
@@ -2928,10 +2928,10 @@
         <v>0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0</v>
+        <v>10009832</v>
       </c>
       <c r="BP10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BQ10" t="n">
         <v>0</v>
@@ -2972,13 +2972,13 @@
         <v>-2</v>
       </c>
       <c r="I11" t="n">
-        <v>1044.7</v>
+        <v>1049.4</v>
       </c>
       <c r="J11" t="n">
         <v>1175.33</v>
       </c>
       <c r="K11" t="n">
-        <v>-11.1</v>
+        <v>-10.7</v>
       </c>
       <c r="L11" t="n">
         <v>69.75</v>
@@ -3015,13 +3015,13 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>2.324</v>
+        <v>2.339</v>
       </c>
       <c r="W11" t="n">
-        <v>2526</v>
+        <v>2510</v>
       </c>
       <c r="X11" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Y11" t="n">
         <v>6</v>
@@ -3048,19 +3048,19 @@
         <v>3.87</v>
       </c>
       <c r="AG11" t="n">
-        <v>1136.54</v>
+        <v>1135</v>
       </c>
       <c r="AH11" t="n">
-        <v>1089.89</v>
+        <v>1089.64</v>
       </c>
       <c r="AI11" t="n">
-        <v>7.4</v>
+        <v>5.4</v>
       </c>
       <c r="AJ11" t="n">
         <v>1175.326204878987</v>
       </c>
       <c r="AK11" t="n">
-        <v>-11.1</v>
+        <v>-10.7</v>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
@@ -3175,12 +3175,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HEXAGON</t>
+          <t>INDORAMA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HEXAGON NUTRITION LIMITED</t>
+          <t>INDO RAMA SYNTHETICS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -3192,40 +3192,40 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G12" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>68.59</v>
+        <v>92.39</v>
       </c>
       <c r="J12" t="n">
-        <v>64.48999999999999</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>6.4</v>
+        <v>22.1</v>
       </c>
       <c r="L12" t="n">
-        <v>64.29000000000001</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>0.57</v>
+        <v>3.14</v>
       </c>
       <c r="N12" t="n">
-        <v>5656038</v>
+        <v>31393588</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>5656038</v>
+        <v>31393588</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -3239,58 +3239,60 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>0.068</v>
+        <v>0.13</v>
       </c>
       <c r="W12" t="n">
-        <v>831</v>
+        <v>2417</v>
       </c>
       <c r="X12" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>19</v>
+        <v>-3</v>
       </c>
       <c r="Z12" t="n">
-        <v>12.31</v>
+        <v>62</v>
       </c>
       <c r="AA12" t="n">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8</v>
+        <v>1.29</v>
       </c>
       <c r="AC12" t="n">
-        <v>22.2</v>
+        <v>15.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.11</v>
+        <v>1.69</v>
       </c>
       <c r="AE12" t="b">
         <v>1</v>
       </c>
       <c r="AF12" t="n">
-        <v>12.14</v>
+        <v>8</v>
       </c>
       <c r="AG12" t="n">
-        <v>66.54000000000001</v>
-      </c>
-      <c r="AH12" t="inlineStr"/>
+        <v>75.67</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>49.86</v>
+      </c>
       <c r="AI12" t="n">
-        <v>35.4</v>
+        <v>163</v>
       </c>
       <c r="AJ12" t="n">
-        <v>64.49302166476625</v>
+        <v>75.6844038997483</v>
       </c>
       <c r="AK12" t="n">
-        <v>6.4</v>
+        <v>22.1</v>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
@@ -3299,32 +3301,32 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>08-09-2026</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="AR12" t="n">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="AS12" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AT12" t="n">
         <v>0</v>
@@ -3333,13 +3335,13 @@
         <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AX12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AY12" t="n">
         <v>0</v>
@@ -3348,13 +3350,13 @@
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>2601121</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>5656038</v>
+        <v>31393588</v>
       </c>
       <c r="BC12" t="n">
-        <v>5656038</v>
+        <v>31393588</v>
       </c>
       <c r="BD12" t="n">
         <v>0</v>
@@ -3390,10 +3392,10 @@
         <v>0</v>
       </c>
       <c r="BO12" t="n">
-        <v>2601121</v>
+        <v>0</v>
       </c>
       <c r="BP12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BQ12" t="n">
         <v>0</v>
@@ -3405,16 +3407,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BHAGERIA</t>
+          <t>HEXAGON</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bhageria Industries Limited</t>
+          <t>HEXAGON NUTRITION LIMITED</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3422,40 +3424,40 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F13" t="n">
         <v>22</v>
       </c>
       <c r="G13" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>367</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>217.8</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>68.5</v>
+        <v>7.7</v>
       </c>
       <c r="L13" t="n">
-        <v>71.75</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>0.82</v>
+        <v>0.57</v>
       </c>
       <c r="N13" t="n">
-        <v>8227124</v>
+        <v>5656038</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>8227124</v>
+        <v>5656038</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -3469,109 +3471,107 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>18-09-2026</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>0.052</v>
+        <v>0.066</v>
       </c>
       <c r="W13" t="n">
-        <v>1597</v>
+        <v>851</v>
       </c>
       <c r="X13" t="n">
         <v>21.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="Z13" t="n">
-        <v>40</v>
+        <v>12.31</v>
       </c>
       <c r="AA13" t="n">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.23</v>
+        <v>0.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>11</v>
+        <v>22.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.01</v>
+        <v>0.11</v>
       </c>
       <c r="AE13" t="b">
         <v>1</v>
       </c>
       <c r="AF13" t="n">
-        <v>14</v>
+        <v>12.14</v>
       </c>
       <c r="AG13" t="n">
-        <v>279.28</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>201.07</v>
-      </c>
+        <v>66.69</v>
+      </c>
+      <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="n">
-        <v>137.4</v>
+        <v>37.1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>217.7985916238683</v>
+        <v>64.49302166476625</v>
       </c>
       <c r="AK13" t="n">
-        <v>68.5</v>
+        <v>7.7</v>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>Aging</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>18-09-2026</t>
         </is>
       </c>
       <c r="AQ13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>53</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
         <v>6</v>
       </c>
-      <c r="AR13" t="n">
-        <v>50</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>44</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
       <c r="AW13" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AX13" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AY13" t="n">
         <v>0</v>
@@ -3580,13 +3580,13 @@
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>2601121</v>
       </c>
       <c r="BB13" t="n">
-        <v>8227124</v>
+        <v>5656038</v>
       </c>
       <c r="BC13" t="n">
-        <v>8227124</v>
+        <v>5656038</v>
       </c>
       <c r="BD13" t="n">
         <v>0</v>
@@ -3622,10 +3622,10 @@
         <v>0</v>
       </c>
       <c r="BO13" t="n">
-        <v>0</v>
+        <v>2601121</v>
       </c>
       <c r="BP13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BQ13" t="n">
         <v>0</v>
@@ -3637,16 +3637,16 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ALEMBICLTD</t>
+          <t>BHAGERIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Alembic Limited</t>
+          <t>Bhageria Industries Limited</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3654,83 +3654,83 @@
         </is>
       </c>
       <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>22</v>
+      </c>
+      <c r="G14" t="n">
+        <v>25</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>364.9</v>
+      </c>
+      <c r="J14" t="n">
+        <v>217.8</v>
+      </c>
+      <c r="K14" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>71.75</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="N14" t="n">
+        <v>8227124</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>8227124</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>5</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>26-08-2026</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1589</v>
+      </c>
+      <c r="X14" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>54</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="AC14" t="n">
         <v>11</v>
-      </c>
-      <c r="F14" t="n">
-        <v>8</v>
-      </c>
-      <c r="G14" t="n">
-        <v>21</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>99.72</v>
-      </c>
-      <c r="J14" t="n">
-        <v>96.81999999999999</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3</v>
-      </c>
-      <c r="L14" t="n">
-        <v>70.88</v>
-      </c>
-      <c r="M14" t="n">
-        <v>14.28</v>
-      </c>
-      <c r="N14" t="n">
-        <v>142781113</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>142781113</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S14" t="b">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>10</v>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>30-09-2026</t>
-        </is>
-      </c>
-      <c r="V14" t="n">
-        <v>0.5580000000000001</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2557</v>
-      </c>
-      <c r="X14" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>-14</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>16.9</v>
       </c>
       <c r="AD14" t="n">
         <v>0.01</v>
@@ -3739,86 +3739,86 @@
         <v>1</v>
       </c>
       <c r="AF14" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="AG14" t="n">
-        <v>98.06999999999999</v>
+        <v>282.45</v>
       </c>
       <c r="AH14" t="n">
-        <v>92.63</v>
+        <v>202</v>
       </c>
       <c r="AI14" t="n">
-        <v>23.5</v>
+        <v>129.2</v>
       </c>
       <c r="AJ14" t="n">
-        <v>96.81860858409144</v>
+        <v>217.7985916238683</v>
       </c>
       <c r="AK14" t="n">
-        <v>3</v>
+        <v>67.5</v>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="AQ14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS14" t="n">
         <v>44</v>
       </c>
-      <c r="AR14" t="n">
-        <v>53</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>9</v>
-      </c>
       <c r="AT14" t="n">
         <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
         <v>5</v>
       </c>
-      <c r="AW14" t="n">
-        <v>10</v>
-      </c>
       <c r="AX14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AY14" t="n">
         <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>20931813</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>57895837</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>142781113</v>
+        <v>8227124</v>
       </c>
       <c r="BC14" t="n">
-        <v>142781113</v>
+        <v>8227124</v>
       </c>
       <c r="BD14" t="n">
         <v>0</v>
@@ -3854,7 +3854,7 @@
         <v>0</v>
       </c>
       <c r="BO14" t="n">
-        <v>57895837</v>
+        <v>0</v>
       </c>
       <c r="BP14" t="n">
         <v>1</v>
@@ -3869,57 +3869,57 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SILVERTUC</t>
+          <t>ALEMBICLTD</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
+          <t>Alembic Limited</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Fundamental Watch</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F15" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>125.98</v>
+        <v>99.25</v>
       </c>
       <c r="J15" t="n">
-        <v>171.54</v>
+        <v>96.81999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>-26.6</v>
+        <v>2.5</v>
       </c>
       <c r="L15" t="n">
-        <v>74.59</v>
+        <v>70.88</v>
       </c>
       <c r="M15" t="n">
-        <v>1.11</v>
+        <v>14.28</v>
       </c>
       <c r="N15" t="n">
-        <v>11081344</v>
+        <v>142781113</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>11081344</v>
+        <v>142781113</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -3941,52 +3941,52 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>0.067</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="W15" t="n">
-        <v>1651</v>
+        <v>2547</v>
       </c>
       <c r="X15" t="n">
-        <v>37.9</v>
+        <v>20.9</v>
       </c>
       <c r="Y15" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="Z15" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AA15" t="n">
-        <v>83</v>
+        <v>-14</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8</v>
+        <v>0.57</v>
       </c>
       <c r="AC15" t="n">
-        <v>30.3</v>
+        <v>16.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="AE15" t="b">
         <v>1</v>
       </c>
       <c r="AF15" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AG15" t="n">
-        <v>171.98</v>
+        <v>98.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>470.93</v>
+        <v>92.61</v>
       </c>
       <c r="AI15" t="n">
-        <v>2</v>
+        <v>15.9</v>
       </c>
       <c r="AJ15" t="n">
-        <v>171.5378328173375</v>
+        <v>96.81860858409144</v>
       </c>
       <c r="AK15" t="n">
-        <v>-26.6</v>
+        <v>2.5</v>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
@@ -4014,10 +4014,10 @@
         </is>
       </c>
       <c r="AQ15" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AR15" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="AS15" t="n">
         <v>9</v>
@@ -4026,31 +4026,31 @@
         <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AW15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AX15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AY15" t="n">
         <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>83720</v>
+        <v>20931813</v>
       </c>
       <c r="BA15" t="n">
-        <v>83720</v>
+        <v>57895837</v>
       </c>
       <c r="BB15" t="n">
-        <v>11081344</v>
+        <v>142781113</v>
       </c>
       <c r="BC15" t="n">
-        <v>11081344</v>
+        <v>142781113</v>
       </c>
       <c r="BD15" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
         <v>0</v>
       </c>
       <c r="BO15" t="n">
-        <v>83720</v>
+        <v>57895837</v>
       </c>
       <c r="BP15" t="n">
         <v>1</v>
@@ -4101,16 +4101,16 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VEEGALAND</t>
+          <t>SILVERTUC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Veegaland Developers Limited</t>
+          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4118,40 +4118,40 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>136.9</v>
+        <v>131.18</v>
       </c>
       <c r="J16" t="n">
-        <v>143.72</v>
+        <v>171.54</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.7</v>
+        <v>-23.5</v>
       </c>
       <c r="L16" t="n">
-        <v>63.69</v>
+        <v>74.59</v>
       </c>
       <c r="M16" t="n">
-        <v>19.68</v>
+        <v>1.11</v>
       </c>
       <c r="N16" t="n">
-        <v>196783125</v>
+        <v>11081344</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>196783125</v>
+        <v>11081344</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -4165,54 +4165,60 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>22-09-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
       <c r="V16" t="n">
-        <v>3.018</v>
+        <v>0.067</v>
       </c>
       <c r="W16" t="n">
-        <v>652</v>
+        <v>1659</v>
       </c>
       <c r="X16" t="n">
-        <v>19.6</v>
+        <v>38.1</v>
       </c>
       <c r="Y16" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="Z16" t="n">
-        <v>13.01</v>
+        <v>17</v>
       </c>
       <c r="AA16" t="n">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.88</v>
+        <v>0.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>14.1</v>
+        <v>30.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
       <c r="AE16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF16" t="n">
-        <v>17.51</v>
-      </c>
-      <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>170.4</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>467.19</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>2.4</v>
+      </c>
       <c r="AJ16" t="n">
-        <v>143.7164139971926</v>
+        <v>171.5378328173375</v>
       </c>
       <c r="AK16" t="n">
-        <v>-4.7</v>
+        <v>-23.5</v>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
@@ -4231,52 +4237,52 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>22-09-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
       <c r="AQ16" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="AR16" t="n">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="AS16" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AT16" t="n">
         <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AW16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY16" t="n">
         <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>83720</v>
       </c>
       <c r="BA16" t="n">
-        <v>196783125</v>
+        <v>83720</v>
       </c>
       <c r="BB16" t="n">
-        <v>196783125</v>
+        <v>11081344</v>
       </c>
       <c r="BC16" t="n">
-        <v>196783125</v>
+        <v>11081344</v>
       </c>
       <c r="BD16" t="n">
         <v>0</v>
@@ -4312,7 +4318,7 @@
         <v>0</v>
       </c>
       <c r="BO16" t="n">
-        <v>196783125</v>
+        <v>83720</v>
       </c>
       <c r="BP16" t="n">
         <v>1</v>
@@ -4327,16 +4333,16 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CHEMBONDCH</t>
+          <t>TAINWALCHM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CHEMBOND CHEMICALS LIMITED</t>
+          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -4344,210 +4350,210 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G17" t="n">
+        <v>21</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>219.26</v>
+      </c>
+      <c r="J17" t="n">
+        <v>210.19</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>67.04000000000001</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="N17" t="n">
+        <v>6171564</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>6171564</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
         <v>14</v>
       </c>
-      <c r="G17" t="n">
-        <v>13</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>219.31</v>
-      </c>
-      <c r="J17" t="n">
-        <v>243.52</v>
-      </c>
-      <c r="K17" t="n">
-        <v>-9.9</v>
-      </c>
-      <c r="L17" t="n">
-        <v>67.65000000000001</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N17" t="n">
-        <v>11080000</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>11080000</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S17" t="b">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>28-09-2026</t>
         </is>
       </c>
       <c r="V17" t="n">
-        <v>0.181</v>
+        <v>0.301</v>
       </c>
       <c r="W17" t="n">
-        <v>612</v>
+        <v>205</v>
       </c>
       <c r="X17" t="n">
-        <v>51.1</v>
+        <v>25.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.99</v>
+        <v>0.03</v>
       </c>
       <c r="AA17" t="n">
-        <v>97</v>
+        <v>16</v>
       </c>
       <c r="AB17" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>209.44</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>197.87</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>210.188815475785</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>18-08-2026</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>28-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ17" t="n">
+        <v>41</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>52</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
         <v>1</v>
       </c>
-      <c r="AC17" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
+      <c r="AV17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>131838</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>2522220</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>6171564</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>6171564</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>2522220</v>
+      </c>
+      <c r="BP17" t="n">
         <v>1</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>16.21</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>252.49</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>191.31</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>52.3</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>243.5164835164835</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>-9.9</v>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>Aging</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Mature Accumulation</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>Mature — Wait for Pullback</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>06-08-2026</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>25-08-2026</t>
-        </is>
-      </c>
-      <c r="AQ17" t="n">
-        <v>19</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>64</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>45</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>4065000</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>11080000</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>2</v>
       </c>
       <c r="BQ17" t="n">
         <v>0</v>
@@ -4559,16 +4565,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>JAYAGROGN</t>
+          <t>VEEGALAND</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Jayant Agro-Organics Limited</t>
+          <t>Veegaland Developers Limited</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -4576,40 +4582,40 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="F18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>208.96</v>
+        <v>133.9</v>
       </c>
       <c r="J18" t="n">
-        <v>232.74</v>
+        <v>143.72</v>
       </c>
       <c r="K18" t="n">
-        <v>-10.2</v>
+        <v>-6.8</v>
       </c>
       <c r="L18" t="n">
-        <v>67.13</v>
+        <v>63.69</v>
       </c>
       <c r="M18" t="n">
-        <v>0.57</v>
+        <v>19.68</v>
       </c>
       <c r="N18" t="n">
-        <v>5704863</v>
+        <v>196783125</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>5704863</v>
+        <v>196783125</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -4627,56 +4633,50 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>22-09-2026</t>
         </is>
       </c>
       <c r="V18" t="n">
-        <v>0.09</v>
+        <v>3.018</v>
       </c>
       <c r="W18" t="n">
-        <v>633</v>
+        <v>652</v>
       </c>
       <c r="X18" t="n">
-        <v>10.3</v>
+        <v>19.7</v>
       </c>
       <c r="Y18" t="n">
-        <v>-5</v>
+        <v>30</v>
       </c>
       <c r="Z18" t="n">
-        <v>32</v>
+        <v>13.01</v>
       </c>
       <c r="AA18" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="AB18" t="n">
-        <v>6.54</v>
+        <v>2.88</v>
       </c>
       <c r="AC18" t="n">
-        <v>14.8</v>
+        <v>14.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.11</v>
+        <v>0.32</v>
       </c>
       <c r="AE18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>226.6</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>205.62</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>12.4</v>
-      </c>
+        <v>17.51</v>
+      </c>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
       <c r="AJ18" t="n">
-        <v>232.7375571148825</v>
+        <v>143.7164139971926</v>
       </c>
       <c r="AK18" t="n">
-        <v>-10.2</v>
+        <v>-6.8</v>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
@@ -4695,22 +4695,22 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>18-09-2026</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>22-09-2026</t>
         </is>
       </c>
       <c r="AQ18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR18" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AS18" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AT18" t="n">
         <v>0</v>
@@ -4734,13 +4734,13 @@
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>5704863</v>
+        <v>196783125</v>
       </c>
       <c r="BB18" t="n">
-        <v>5704863</v>
+        <v>196783125</v>
       </c>
       <c r="BC18" t="n">
-        <v>5704863</v>
+        <v>196783125</v>
       </c>
       <c r="BD18" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
         <v>0</v>
       </c>
       <c r="BO18" t="n">
-        <v>5704863</v>
+        <v>196783125</v>
       </c>
       <c r="BP18" t="n">
         <v>1</v>
@@ -4791,16 +4791,16 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BERGEPAINT</t>
+          <t>CHEMBONDCH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BERGER PAINTS (I) LIMITED</t>
+          <t>CHEMBOND CHEMICALS LIMITED</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4808,107 +4808,107 @@
         </is>
       </c>
       <c r="E19" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" t="n">
+        <v>14</v>
+      </c>
+      <c r="G19" t="n">
+        <v>13</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>220.86</v>
+      </c>
+      <c r="J19" t="n">
+        <v>243.52</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="L19" t="n">
+        <v>67.65000000000001</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N19" t="n">
+        <v>11080000</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>11080000</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
         <v>3</v>
       </c>
-      <c r="F19" t="n">
-        <v>16</v>
-      </c>
-      <c r="G19" t="n">
-        <v>9</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>467.95</v>
-      </c>
-      <c r="J19" t="n">
-        <v>489.56</v>
-      </c>
-      <c r="K19" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="L19" t="n">
-        <v>75</v>
-      </c>
-      <c r="M19" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="N19" t="n">
-        <v>48436318</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>48436318</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S19" t="b">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>5</v>
-      </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>07-09-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="V19" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.191</v>
       </c>
       <c r="W19" t="n">
-        <v>55105</v>
+        <v>581</v>
       </c>
       <c r="X19" t="n">
-        <v>46.7</v>
+        <v>48.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z19" t="n">
-        <v>562</v>
+        <v>2.99</v>
       </c>
       <c r="AA19" t="n">
-        <v>8</v>
+        <v>97</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.16</v>
+        <v>1</v>
       </c>
       <c r="AC19" t="n">
-        <v>22.9</v>
+        <v>11.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>1</v>
       </c>
       <c r="AF19" t="n">
-        <v>17</v>
+        <v>16.21</v>
       </c>
       <c r="AG19" t="n">
-        <v>494.45</v>
+        <v>252.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>488.73</v>
+        <v>191.63</v>
       </c>
       <c r="AI19" t="n">
-        <v>8.9</v>
+        <v>50.2</v>
       </c>
       <c r="AJ19" t="n">
-        <v>489.5623319654733</v>
+        <v>243.5164835164835</v>
       </c>
       <c r="AK19" t="n">
-        <v>-4.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
@@ -4927,22 +4927,22 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>07-09-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>07-09-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AR19" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="AS19" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="AT19" t="n">
         <v>0</v>
@@ -4954,10 +4954,10 @@
         <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AX19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY19" t="n">
         <v>0</v>
@@ -4969,10 +4969,10 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>48436318</v>
+        <v>4065000</v>
       </c>
       <c r="BC19" t="n">
-        <v>48436318</v>
+        <v>11080000</v>
       </c>
       <c r="BD19" t="n">
         <v>0</v>
@@ -5011,7 +5011,7 @@
         <v>0</v>
       </c>
       <c r="BP19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BQ19" t="n">
         <v>0</v>
@@ -5023,16 +5023,16 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BMWVENTLTD</t>
+          <t>JAYAGROGN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BMW VENTURES LIMITED</t>
+          <t>Jayant Agro-Organics Limited</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -5040,40 +5040,40 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F20" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>49.72</v>
+        <v>212.86</v>
       </c>
       <c r="J20" t="n">
-        <v>55.06</v>
+        <v>232.74</v>
       </c>
       <c r="K20" t="n">
-        <v>-9.699999999999999</v>
+        <v>-8.5</v>
       </c>
       <c r="L20" t="n">
-        <v>73.01000000000001</v>
+        <v>67.13</v>
       </c>
       <c r="M20" t="n">
-        <v>2.9</v>
+        <v>0.57</v>
       </c>
       <c r="N20" t="n">
-        <v>28991535</v>
+        <v>5704863</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>28991535</v>
+        <v>5704863</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -5087,60 +5087,60 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>22-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="V20" t="n">
-        <v>0.616</v>
+        <v>0.089</v>
       </c>
       <c r="W20" t="n">
-        <v>471</v>
+        <v>642</v>
       </c>
       <c r="X20" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="Y20" t="n">
-        <v>19</v>
+        <v>-5</v>
       </c>
       <c r="Z20" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="AA20" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.22</v>
+        <v>6.54</v>
       </c>
       <c r="AC20" t="n">
-        <v>12</v>
+        <v>14.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.58</v>
+        <v>0.11</v>
       </c>
       <c r="AE20" t="b">
         <v>1</v>
       </c>
       <c r="AF20" t="n">
-        <v>3.4</v>
+        <v>9</v>
       </c>
       <c r="AG20" t="n">
-        <v>54.96</v>
+        <v>226.38</v>
       </c>
       <c r="AH20" t="n">
-        <v>57.64</v>
+        <v>205.68</v>
       </c>
       <c r="AI20" t="n">
-        <v>-8.699999999999999</v>
+        <v>10.8</v>
       </c>
       <c r="AJ20" t="n">
-        <v>55.06464387464388</v>
+        <v>232.7375571148825</v>
       </c>
       <c r="AK20" t="n">
-        <v>-9.699999999999999</v>
+        <v>-8.5</v>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
@@ -5159,22 +5159,22 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>22-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="AQ20" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="AR20" t="n">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="AS20" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AT20" t="n">
         <v>0</v>
@@ -5183,13 +5183,13 @@
         <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW20" t="n">
         <v>4</v>
       </c>
       <c r="AX20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY20" t="n">
         <v>0</v>
@@ -5198,13 +5198,13 @@
         <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>10009832</v>
+        <v>5704863</v>
       </c>
       <c r="BB20" t="n">
-        <v>19968394</v>
+        <v>5704863</v>
       </c>
       <c r="BC20" t="n">
-        <v>28991535</v>
+        <v>5704863</v>
       </c>
       <c r="BD20" t="n">
         <v>0</v>
@@ -5240,7 +5240,7 @@
         <v>0</v>
       </c>
       <c r="BO20" t="n">
-        <v>10009832</v>
+        <v>5704863</v>
       </c>
       <c r="BP20" t="n">
         <v>1</v>
@@ -5255,16 +5255,16 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HTEL</t>
+          <t>BERGEPAINT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers Limited</t>
+          <t>BERGER PAINTS (I) LIMITED</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5275,37 +5275,37 @@
         <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>97.27</v>
+        <v>471.9</v>
       </c>
       <c r="J21" t="n">
-        <v>68.68000000000001</v>
+        <v>489.56</v>
       </c>
       <c r="K21" t="n">
-        <v>41.6</v>
+        <v>-3.6</v>
       </c>
       <c r="L21" t="n">
-        <v>71.22</v>
+        <v>75</v>
       </c>
       <c r="M21" t="n">
-        <v>0.86</v>
+        <v>4.84</v>
       </c>
       <c r="N21" t="n">
-        <v>8585000</v>
+        <v>48436318</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>8585000</v>
+        <v>48436318</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -5319,58 +5319,64 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="V21" t="n">
-        <v>0.1</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="W21" t="n">
-        <v>861</v>
+        <v>55030</v>
       </c>
       <c r="X21" t="n">
-        <v>37.5</v>
+        <v>46.6</v>
       </c>
       <c r="Y21" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.44</v>
+        <v>562</v>
       </c>
       <c r="AA21" t="n">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.55</v>
+        <v>3.16</v>
       </c>
       <c r="AC21" t="n">
-        <v>23.9</v>
+        <v>22.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.25</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AE21" t="b">
         <v>1</v>
       </c>
       <c r="AF21" t="n">
-        <v>19.61</v>
-      </c>
-      <c r="AG21" t="inlineStr"/>
-      <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>493.49</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>488.39</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>8.300000000000001</v>
+      </c>
       <c r="AJ21" t="n">
-        <v>68.68000000000001</v>
+        <v>489.5623319654733</v>
       </c>
       <c r="AK21" t="n">
-        <v>41.6</v>
+        <v>-3.6</v>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -5380,57 +5386,57 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="AQ21" t="n">
         <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="AS21" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="AT21" t="n">
         <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AX21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AY21" t="n">
         <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>8585000</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>8585000</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>8585000</v>
+        <v>48436318</v>
       </c>
       <c r="BC21" t="n">
-        <v>8585000</v>
+        <v>48436318</v>
       </c>
       <c r="BD21" t="n">
         <v>0</v>
@@ -5466,10 +5472,10 @@
         <v>0</v>
       </c>
       <c r="BO21" t="n">
-        <v>8585000</v>
+        <v>0</v>
       </c>
       <c r="BP21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BQ21" t="n">
         <v>0</v>
@@ -5481,120 +5487,118 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SRGHFL</t>
+          <t>HTEL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SRG HOUSING FINANCE LIMITED</t>
+          <t>Hy-Tech Engineers Limited</t>
         </is>
       </c>
       <c r="C22" t="n">
+        <v>18</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="n">
+        <v>22</v>
+      </c>
+      <c r="G22" t="n">
+        <v>4</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>90.37</v>
+      </c>
+      <c r="J22" t="n">
+        <v>68.68000000000001</v>
+      </c>
+      <c r="K22" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="L22" t="n">
+        <v>71.22</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="N22" t="n">
+        <v>8585000</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>8585000</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>29-09-2026</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W22" t="n">
+        <v>861</v>
+      </c>
+      <c r="X22" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="Y22" t="n">
         <v>17</v>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Avoid</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>15</v>
-      </c>
-      <c r="F22" t="n">
-        <v>7</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>120.97</v>
-      </c>
-      <c r="J22" t="n">
-        <v>132.2</v>
-      </c>
-      <c r="K22" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="L22" t="n">
-        <v>67.83</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="N22" t="n">
-        <v>19830410</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>19830410</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S22" t="b">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3</v>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>16-09-2026</t>
-        </is>
-      </c>
-      <c r="V22" t="n">
-        <v>1.096</v>
-      </c>
-      <c r="W22" t="n">
-        <v>181</v>
-      </c>
-      <c r="X22" t="n">
-        <v>5.28</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>31</v>
-      </c>
-      <c r="Z22" t="inlineStr"/>
+      <c r="Z22" t="n">
+        <v>8.44</v>
+      </c>
       <c r="AA22" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="AB22" t="n">
-        <v>5.39</v>
+        <v>0.55</v>
       </c>
       <c r="AC22" t="n">
-        <v>11.8</v>
+        <v>23.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.89</v>
+        <v>0.25</v>
       </c>
       <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="inlineStr"/>
-      <c r="AG22" t="n">
-        <v>219.18</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>264.31</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>-53.9</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>19.61</v>
+      </c>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
       <c r="AJ22" t="n">
-        <v>132.2027333333333</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="AK22" t="n">
-        <v>-8.5</v>
+        <v>31.6</v>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
@@ -5603,62 +5607,62 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>15-09-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
         <v>1</v>
       </c>
-      <c r="AR22" t="n">
-        <v>24</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>23</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>0</v>
-      </c>
       <c r="AV22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AW22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AX22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>8585000</v>
       </c>
       <c r="BA22" t="n">
-        <v>19830410</v>
+        <v>8585000</v>
       </c>
       <c r="BB22" t="n">
-        <v>19830410</v>
+        <v>8585000</v>
       </c>
       <c r="BC22" t="n">
-        <v>19830410</v>
+        <v>8585000</v>
       </c>
       <c r="BD22" t="n">
         <v>0</v>
@@ -5694,10 +5698,10 @@
         <v>0</v>
       </c>
       <c r="BO22" t="n">
-        <v>19830410</v>
+        <v>8585000</v>
       </c>
       <c r="BP22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ22" t="n">
         <v>0</v>
@@ -5709,12 +5713,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TAINWALCHM</t>
+          <t>SRGHFL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
+          <t>SRG HOUSING FINANCE LIMITED</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -5726,40 +5730,40 @@
         </is>
       </c>
       <c r="E23" t="n">
+        <v>15</v>
+      </c>
+      <c r="F23" t="n">
         <v>7</v>
       </c>
-      <c r="F23" t="n">
-        <v>6</v>
-      </c>
       <c r="G23" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>203.35</v>
+        <v>115.81</v>
       </c>
       <c r="J23" t="n">
-        <v>210.19</v>
+        <v>132.2</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.3</v>
+        <v>-12.4</v>
       </c>
       <c r="L23" t="n">
-        <v>67.04000000000001</v>
+        <v>67.83</v>
       </c>
       <c r="M23" t="n">
-        <v>0.62</v>
+        <v>1.98</v>
       </c>
       <c r="N23" t="n">
-        <v>6171564</v>
+        <v>19830410</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>6171564</v>
+        <v>19830410</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -5773,60 +5777,56 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>28-09-2026</t>
+          <t>16-09-2026</t>
         </is>
       </c>
       <c r="V23" t="n">
-        <v>0.335</v>
+        <v>1.09</v>
       </c>
       <c r="W23" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="X23" t="n">
-        <v>22.8</v>
+        <v>5.33</v>
       </c>
       <c r="Y23" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0.03</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.03</v>
+        <v>5.39</v>
       </c>
       <c r="AC23" t="n">
-        <v>7.91</v>
+        <v>11.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="n">
-        <v>3.16</v>
-      </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="n">
-        <v>208.98</v>
+        <v>215.63</v>
       </c>
       <c r="AH23" t="n">
-        <v>197.84</v>
+        <v>263.57</v>
       </c>
       <c r="AI23" t="n">
-        <v>13.5</v>
+        <v>-56.5</v>
       </c>
       <c r="AJ23" t="n">
-        <v>210.188815475785</v>
+        <v>132.2027333333333</v>
       </c>
       <c r="AK23" t="n">
-        <v>-3.3</v>
+        <v>-12.4</v>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
@@ -5845,52 +5845,52 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>18-08-2026</t>
+          <t>15-09-2026</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>28-09-2026</t>
+          <t>16-09-2026</t>
         </is>
       </c>
       <c r="AQ23" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="AR23" t="n">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="AS23" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="AT23" t="n">
         <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AW23" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="AX23" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="AY23" t="n">
         <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>131838</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>2522220</v>
+        <v>19830410</v>
       </c>
       <c r="BB23" t="n">
-        <v>6171564</v>
+        <v>19830410</v>
       </c>
       <c r="BC23" t="n">
-        <v>6171564</v>
+        <v>19830410</v>
       </c>
       <c r="BD23" t="n">
         <v>0</v>
@@ -5926,10 +5926,10 @@
         <v>0</v>
       </c>
       <c r="BO23" t="n">
-        <v>2522220</v>
+        <v>19830410</v>
       </c>
       <c r="BP23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ23" t="n">
         <v>0</v>
@@ -5970,13 +5970,13 @@
         <v>-1</v>
       </c>
       <c r="I24" t="n">
-        <v>567.75</v>
+        <v>545.25</v>
       </c>
       <c r="J24" t="n">
         <v>638.11</v>
       </c>
       <c r="K24" t="n">
-        <v>-11</v>
+        <v>-14.6</v>
       </c>
       <c r="L24" t="n">
         <v>64.68000000000001</v>
@@ -6013,13 +6013,13 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>0.387</v>
+        <v>0.386</v>
       </c>
       <c r="W24" t="n">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="X24" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
       <c r="Y24" t="n">
         <v>21</v>
@@ -6046,19 +6046,19 @@
         <v>-110</v>
       </c>
       <c r="AG24" t="n">
-        <v>594.48</v>
+        <v>594.36</v>
       </c>
       <c r="AH24" t="n">
-        <v>519.4299999999999</v>
+        <v>519.4</v>
       </c>
       <c r="AI24" t="n">
-        <v>18.9</v>
+        <v>12</v>
       </c>
       <c r="AJ24" t="n">
         <v>638.108361041278</v>
       </c>
       <c r="AK24" t="n">
-        <v>-11</v>
+        <v>-14.6</v>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
@@ -6173,16 +6173,16 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SINCLAIR</t>
+          <t>WCIL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SINCLAIRS HOTELS LIMITED</t>
+          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -6190,171 +6190,171 @@
         </is>
       </c>
       <c r="E25" t="n">
+        <v>7</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>13</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>97.52</v>
+      </c>
+      <c r="J25" t="n">
+        <v>96.03</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L25" t="n">
+        <v>71.89</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N25" t="n">
+        <v>26023230</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>26023230</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>29-09-2026</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1001</v>
+      </c>
+      <c r="X25" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>18.68</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-36</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>89.18000000000001</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>100.01</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>96.02667896678967</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>18-09-2026</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>29-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ25" t="n">
         <v>11</v>
       </c>
-      <c r="F25" t="n">
-        <v>8</v>
-      </c>
-      <c r="G25" t="n">
-        <v>4</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>74.83</v>
-      </c>
-      <c r="J25" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="K25" t="n">
-        <v>-7.7</v>
-      </c>
-      <c r="L25" t="n">
-        <v>62.78</v>
-      </c>
-      <c r="M25" t="n">
-        <v>2</v>
-      </c>
-      <c r="N25" t="n">
-        <v>19959718</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>19959718</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S25" t="b">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>8</v>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>24-09-2026</t>
-        </is>
-      </c>
-      <c r="V25" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="W25" t="n">
-        <v>384</v>
-      </c>
-      <c r="X25" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="Y25" t="n">
+      <c r="AR25" t="n">
         <v>21</v>
       </c>
-      <c r="Z25" t="n">
-        <v>8.390000000000001</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>-19</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>8.73</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="AE25" t="b">
+      <c r="AS25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
         <v>1</v>
       </c>
-      <c r="AF25" t="n">
-        <v>41.64</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>78.09</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>77.58</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>81.10277768748172</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>-7.7</v>
-      </c>
-      <c r="AL25" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>28-08-2026</t>
-        </is>
-      </c>
-      <c r="AP25" t="inlineStr">
-        <is>
-          <t>24-09-2026</t>
-        </is>
-      </c>
-      <c r="AQ25" t="n">
-        <v>27</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>42</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>15</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>0</v>
-      </c>
       <c r="AV25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW25" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AX25" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AY25" t="n">
         <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>6202680</v>
       </c>
       <c r="BA25" t="n">
-        <v>2802843</v>
+        <v>26023230</v>
       </c>
       <c r="BB25" t="n">
-        <v>19959718</v>
+        <v>26023230</v>
       </c>
       <c r="BC25" t="n">
-        <v>19959718</v>
+        <v>26023230</v>
       </c>
       <c r="BD25" t="n">
         <v>0</v>
@@ -6390,7 +6390,7 @@
         <v>0</v>
       </c>
       <c r="BO25" t="n">
-        <v>2802843</v>
+        <v>26023230</v>
       </c>
       <c r="BP25" t="n">
         <v>1</v>
@@ -6405,12 +6405,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AFFORDABLE</t>
+          <t>SINCLAIR</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AFFORDABLE ROBOTIC &amp; AUTOMATION LIMITED</t>
+          <t>SINCLAIRS HOTELS LIMITED</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -6425,37 +6425,37 @@
         <v>11</v>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H26" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>158.28</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>174.27</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>-9.199999999999999</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>61.48</v>
+        <v>62.78</v>
       </c>
       <c r="M26" t="n">
-        <v>1.07</v>
+        <v>2</v>
       </c>
       <c r="N26" t="n">
-        <v>10743104</v>
+        <v>19959718</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>10743104</v>
+        <v>19959718</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -6469,7 +6469,7 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
@@ -6477,52 +6477,52 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>0.524</v>
+        <v>0.517</v>
       </c>
       <c r="W26" t="n">
-        <v>205</v>
+        <v>386</v>
       </c>
       <c r="X26" t="n">
-        <v>35.6</v>
+        <v>35.8</v>
       </c>
       <c r="Y26" t="n">
-        <v>-44</v>
+        <v>21</v>
       </c>
       <c r="Z26" t="n">
-        <v>-3.28</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="AA26" t="n">
-        <v>141</v>
+        <v>-19</v>
       </c>
       <c r="AB26" t="n">
-        <v>-4.05</v>
+        <v>1.54</v>
       </c>
       <c r="AC26" t="n">
-        <v>8.25</v>
+        <v>8.73</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.44</v>
+        <v>0.28</v>
       </c>
       <c r="AE26" t="b">
         <v>1</v>
       </c>
       <c r="AF26" t="n">
-        <v>-35.96</v>
+        <v>41.64</v>
       </c>
       <c r="AG26" t="n">
-        <v>170.93</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="AH26" t="n">
-        <v>177.23</v>
+        <v>77.54000000000001</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.7</v>
+        <v>-4.5</v>
       </c>
       <c r="AJ26" t="n">
-        <v>174.2652478588113</v>
+        <v>81.10277768748172</v>
       </c>
       <c r="AK26" t="n">
-        <v>-9.199999999999999</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
@@ -6550,10 +6550,10 @@
         </is>
       </c>
       <c r="AQ26" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AR26" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="AS26" t="n">
         <v>15</v>
@@ -6565,13 +6565,13 @@
         <v>0</v>
       </c>
       <c r="AV26" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AW26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY26" t="n">
         <v>0</v>
@@ -6580,13 +6580,13 @@
         <v>0</v>
       </c>
       <c r="BA26" t="n">
-        <v>10743104</v>
+        <v>2802843</v>
       </c>
       <c r="BB26" t="n">
-        <v>10743104</v>
+        <v>19959718</v>
       </c>
       <c r="BC26" t="n">
-        <v>10743104</v>
+        <v>19959718</v>
       </c>
       <c r="BD26" t="n">
         <v>0</v>
@@ -6622,7 +6622,7 @@
         <v>0</v>
       </c>
       <c r="BO26" t="n">
-        <v>10743104</v>
+        <v>2802843</v>
       </c>
       <c r="BP26" t="n">
         <v>1</v>
@@ -6666,13 +6666,13 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>150.66</v>
+        <v>152.08</v>
       </c>
       <c r="J27" t="n">
         <v>166</v>
       </c>
       <c r="K27" t="n">
-        <v>-9.199999999999999</v>
+        <v>-8.4</v>
       </c>
       <c r="L27" t="n">
         <v>64.08</v>
@@ -6742,19 +6742,19 @@
         <v>11</v>
       </c>
       <c r="AG27" t="n">
-        <v>164.15</v>
+        <v>163.84</v>
       </c>
       <c r="AH27" t="n">
-        <v>187.02</v>
+        <v>186.6</v>
       </c>
       <c r="AI27" t="n">
-        <v>-24</v>
+        <v>-25.5</v>
       </c>
       <c r="AJ27" t="n">
         <v>165.9960373443983</v>
       </c>
       <c r="AK27" t="n">
-        <v>-9.199999999999999</v>
+        <v>-8.4</v>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
@@ -6898,13 +6898,13 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>416</v>
+        <v>414.5</v>
       </c>
       <c r="J28" t="n">
         <v>417.34</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.3</v>
+        <v>-0.7</v>
       </c>
       <c r="L28" t="n">
         <v>61.75</v>
@@ -6944,10 +6944,10 @@
         <v>0.042</v>
       </c>
       <c r="W28" t="n">
-        <v>1650</v>
+        <v>1631</v>
       </c>
       <c r="X28" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="Y28" t="n">
         <v>10</v>
@@ -6974,19 +6974,19 @@
         <v>12</v>
       </c>
       <c r="AG28" t="n">
-        <v>427.74</v>
+        <v>427.17</v>
       </c>
       <c r="AH28" t="n">
-        <v>473.66</v>
+        <v>472.98</v>
       </c>
       <c r="AI28" t="n">
-        <v>-6.6</v>
+        <v>-8.5</v>
       </c>
       <c r="AJ28" t="n">
         <v>417.3421638870492</v>
       </c>
       <c r="AK28" t="n">
-        <v>-0.3</v>
+        <v>-0.7</v>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
@@ -7101,16 +7101,16 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>WCIL</t>
+          <t>OBCL</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
+          <t>OBCL LIMITED</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -7118,40 +7118,40 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="G29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H29" t="n">
         <v>-1</v>
       </c>
       <c r="I29" t="n">
-        <v>93.3</v>
+        <v>55.19</v>
       </c>
       <c r="J29" t="n">
-        <v>96.03</v>
+        <v>54.07</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.8</v>
+        <v>2.1</v>
       </c>
       <c r="L29" t="n">
-        <v>71.89</v>
+        <v>67.23</v>
       </c>
       <c r="M29" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="N29" t="n">
-        <v>26023230</v>
+        <v>21953383</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>26023230</v>
+        <v>21953383</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -7165,60 +7165,58 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
+        <v>13</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>24-09-2026</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>1.893</v>
+      </c>
+      <c r="W29" t="n">
+        <v>116</v>
+      </c>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-3779</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF29" t="n">
         <v>3</v>
       </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>29-09-2026</t>
-        </is>
-      </c>
-      <c r="V29" t="n">
-        <v>0.263</v>
-      </c>
-      <c r="W29" t="n">
-        <v>989</v>
-      </c>
-      <c r="X29" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>18.68</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>-36</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>6.83</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>4.02</v>
-      </c>
       <c r="AG29" t="n">
-        <v>89.02</v>
+        <v>55.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>100.12</v>
+        <v>55.25</v>
       </c>
       <c r="AI29" t="n">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>96.02667896678967</v>
+        <v>54.06877621438969</v>
       </c>
       <c r="AK29" t="n">
-        <v>-2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
@@ -7237,52 +7235,52 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="AQ29" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="AR29" t="n">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="AS29" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW29" t="n">
         <v>10</v>
       </c>
-      <c r="AT29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>3</v>
-      </c>
       <c r="AX29" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AY29" t="n">
         <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>6202680</v>
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>26023230</v>
+        <v>3549124</v>
       </c>
       <c r="BB29" t="n">
-        <v>26023230</v>
+        <v>18014237</v>
       </c>
       <c r="BC29" t="n">
-        <v>26023230</v>
+        <v>21953383</v>
       </c>
       <c r="BD29" t="n">
         <v>0</v>
@@ -7318,7 +7316,7 @@
         <v>0</v>
       </c>
       <c r="BO29" t="n">
-        <v>26023230</v>
+        <v>3549124</v>
       </c>
       <c r="BP29" t="n">
         <v>1</v>
@@ -7333,57 +7331,57 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>OBCL</t>
+          <t>AFFORDABLE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>OBCL LIMITED</t>
+          <t>AFFORDABLE ROBOTIC &amp; AUTOMATION LIMITED</t>
         </is>
       </c>
       <c r="C30" t="n">
+        <v>10</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
         <v>11</v>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Avoid</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>17</v>
-      </c>
       <c r="F30" t="n">
-        <v>-5</v>
+        <v>3</v>
       </c>
       <c r="G30" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>-1</v>
       </c>
       <c r="I30" t="n">
-        <v>54.84</v>
+        <v>159.8</v>
       </c>
       <c r="J30" t="n">
-        <v>54.07</v>
+        <v>174.27</v>
       </c>
       <c r="K30" t="n">
-        <v>1.4</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="L30" t="n">
-        <v>67.23</v>
+        <v>61.48</v>
       </c>
       <c r="M30" t="n">
-        <v>2.2</v>
+        <v>1.07</v>
       </c>
       <c r="N30" t="n">
-        <v>21953383</v>
+        <v>10743104</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>21953383</v>
+        <v>10743104</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -7397,7 +7395,7 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
@@ -7405,50 +7403,52 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>1.909</v>
+        <v>0.532</v>
       </c>
       <c r="W30" t="n">
-        <v>115</v>
-      </c>
-      <c r="X30" t="inlineStr"/>
+        <v>202</v>
+      </c>
+      <c r="X30" t="n">
+        <v>35</v>
+      </c>
       <c r="Y30" t="n">
-        <v>6</v>
+        <v>-44</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.47</v>
+        <v>-3.28</v>
       </c>
       <c r="AA30" t="n">
-        <v>-3779</v>
+        <v>141</v>
       </c>
       <c r="AB30" t="n">
-        <v>-0.05</v>
+        <v>-4.05</v>
       </c>
       <c r="AC30" t="n">
-        <v>-1.26</v>
+        <v>8.25</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.8</v>
+        <v>0.44</v>
       </c>
       <c r="AE30" t="b">
         <v>1</v>
       </c>
       <c r="AF30" t="n">
-        <v>3</v>
+        <v>-35.96</v>
       </c>
       <c r="AG30" t="n">
-        <v>55.27</v>
+        <v>170.56</v>
       </c>
       <c r="AH30" t="n">
-        <v>55.25</v>
+        <v>176.96</v>
       </c>
       <c r="AI30" t="n">
-        <v>-2.4</v>
+        <v>-4.4</v>
       </c>
       <c r="AJ30" t="n">
-        <v>54.06877621438969</v>
+        <v>174.2652478588113</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.4</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>16-09-2026</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
@@ -7476,10 +7476,10 @@
         </is>
       </c>
       <c r="AQ30" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="AR30" t="n">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="AS30" t="n">
         <v>15</v>
@@ -7491,13 +7491,13 @@
         <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AW30" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AX30" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AY30" t="n">
         <v>0</v>
@@ -7506,13 +7506,13 @@
         <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>3549124</v>
+        <v>10743104</v>
       </c>
       <c r="BB30" t="n">
-        <v>18014237</v>
+        <v>10743104</v>
       </c>
       <c r="BC30" t="n">
-        <v>21953383</v>
+        <v>10743104</v>
       </c>
       <c r="BD30" t="n">
         <v>0</v>
@@ -7548,7 +7548,7 @@
         <v>0</v>
       </c>
       <c r="BO30" t="n">
-        <v>3549124</v>
+        <v>10743104</v>
       </c>
       <c r="BP30" t="n">
         <v>1</v>
@@ -7572,7 +7572,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -7586,19 +7586,19 @@
         <v>-2</v>
       </c>
       <c r="G31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="J31" t="n">
         <v>2.82</v>
       </c>
       <c r="K31" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="L31" t="n">
         <v>64.45</v>
@@ -7668,13 +7668,13 @@
         <v>3.16</v>
       </c>
       <c r="AI31" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
         <v>2.817550384346611</v>
       </c>
       <c r="AK31" t="n">
-        <v>11.1</v>
+        <v>13.6</v>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
@@ -7789,16 +7789,16 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AVONMORE</t>
+          <t>TIGERLOGS</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
+          <t>Tiger Logistics (India) Limited</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -7806,40 +7806,40 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>-1</v>
       </c>
       <c r="I32" t="n">
-        <v>12.43</v>
+        <v>23.59</v>
       </c>
       <c r="J32" t="n">
-        <v>12.86</v>
+        <v>27.53</v>
       </c>
       <c r="K32" t="n">
-        <v>-3.3</v>
+        <v>-14.3</v>
       </c>
       <c r="L32" t="n">
-        <v>69.12</v>
+        <v>61.81</v>
       </c>
       <c r="M32" t="n">
-        <v>2.35</v>
+        <v>0.65</v>
       </c>
       <c r="N32" t="n">
-        <v>23479616</v>
+        <v>6470400</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>23479616</v>
+        <v>6470400</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -7853,56 +7853,60 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
       <c r="V32" t="n">
-        <v>0.677</v>
+        <v>0.26</v>
       </c>
       <c r="W32" t="n">
-        <v>347</v>
+        <v>249</v>
       </c>
       <c r="X32" t="n">
-        <v>1121</v>
+        <v>13.2</v>
       </c>
       <c r="Y32" t="n">
-        <v>-61</v>
-      </c>
-      <c r="Z32" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.79</v>
+      </c>
       <c r="AA32" t="n">
-        <v>-98</v>
+        <v>-30</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.01</v>
+        <v>0.21</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.46</v>
+        <v>18</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.44</v>
+        <v>0.32</v>
       </c>
       <c r="AE32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF32" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.83</v>
+      </c>
       <c r="AG32" t="n">
-        <v>12.74</v>
+        <v>27.29</v>
       </c>
       <c r="AH32" t="n">
-        <v>12.96</v>
+        <v>31.57</v>
       </c>
       <c r="AI32" t="n">
-        <v>5.9</v>
+        <v>-15.7</v>
       </c>
       <c r="AJ32" t="n">
-        <v>12.85608234597773</v>
+        <v>27.53361702127659</v>
       </c>
       <c r="AK32" t="n">
-        <v>-3.3</v>
+        <v>-14.3</v>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
@@ -7921,52 +7925,52 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>10-08-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
       <c r="AQ32" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="AR32" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="AS32" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AT32" t="n">
         <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV32" t="n">
         <v>6</v>
       </c>
       <c r="AW32" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="AX32" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="AY32" t="n">
         <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>2256400</v>
       </c>
       <c r="BA32" t="n">
-        <v>5273610</v>
+        <v>4267650</v>
       </c>
       <c r="BB32" t="n">
-        <v>20093495</v>
+        <v>6470400</v>
       </c>
       <c r="BC32" t="n">
-        <v>23479616</v>
+        <v>6470400</v>
       </c>
       <c r="BD32" t="n">
         <v>0</v>
@@ -8002,7 +8006,7 @@
         <v>0</v>
       </c>
       <c r="BO32" t="n">
-        <v>5273610</v>
+        <v>4267650</v>
       </c>
       <c r="BP32" t="n">
         <v>1</v>
@@ -8017,16 +8021,16 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TIGERLOGS</t>
+          <t>LAOPALA</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tiger Logistics (India) Limited</t>
+          <t>LA OPALA RG LIMITED</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -8034,40 +8038,40 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>24.88</v>
+        <v>154.76</v>
       </c>
       <c r="J33" t="n">
-        <v>27.53</v>
+        <v>159.62</v>
       </c>
       <c r="K33" t="n">
-        <v>-9.6</v>
+        <v>-3</v>
       </c>
       <c r="L33" t="n">
-        <v>61.81</v>
+        <v>65.64</v>
       </c>
       <c r="M33" t="n">
-        <v>0.65</v>
+        <v>3.99</v>
       </c>
       <c r="N33" t="n">
-        <v>6470400</v>
+        <v>39906048</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>6470400</v>
+        <v>39906048</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -8081,60 +8085,60 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
       <c r="V33" t="n">
-        <v>0.255</v>
+        <v>0.232</v>
       </c>
       <c r="W33" t="n">
-        <v>254</v>
+        <v>1719</v>
       </c>
       <c r="X33" t="n">
-        <v>13.4</v>
+        <v>18.2</v>
       </c>
       <c r="Y33" t="n">
-        <v>16</v>
+        <v>-3</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.79</v>
+        <v>26</v>
       </c>
       <c r="AA33" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.21</v>
+        <v>2.36</v>
       </c>
       <c r="AC33" t="n">
-        <v>18</v>
+        <v>14.2</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.32</v>
+        <v>0.01</v>
       </c>
       <c r="AE33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.83</v>
+        <v>36</v>
       </c>
       <c r="AG33" t="n">
-        <v>27.42</v>
+        <v>172.06</v>
       </c>
       <c r="AH33" t="n">
-        <v>31.64</v>
+        <v>183.3</v>
       </c>
       <c r="AI33" t="n">
-        <v>-6.1</v>
+        <v>-11.1</v>
       </c>
       <c r="AJ33" t="n">
-        <v>27.53361702127659</v>
+        <v>159.624192</v>
       </c>
       <c r="AK33" t="n">
-        <v>-9.6</v>
+        <v>-3</v>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
@@ -8153,52 +8157,52 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>16-09-2026</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
       <c r="AQ33" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="AR33" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="AS33" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="AT33" t="n">
         <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AW33" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AX33" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AY33" t="n">
         <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>2256400</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>4267650</v>
+        <v>39906048</v>
       </c>
       <c r="BB33" t="n">
-        <v>6470400</v>
+        <v>39906048</v>
       </c>
       <c r="BC33" t="n">
-        <v>6470400</v>
+        <v>39906048</v>
       </c>
       <c r="BD33" t="n">
         <v>0</v>
@@ -8234,7 +8238,7 @@
         <v>0</v>
       </c>
       <c r="BO33" t="n">
-        <v>4267650</v>
+        <v>39906048</v>
       </c>
       <c r="BP33" t="n">
         <v>1</v>
@@ -8249,12 +8253,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>LAOPALA</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LA OPALA RG LIMITED</t>
+          <t>ENVIRO INFRA ENGINEERS LIMITED</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -8266,40 +8270,40 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>153.98</v>
+        <v>179.96</v>
       </c>
       <c r="J34" t="n">
-        <v>159.62</v>
+        <v>191.87</v>
       </c>
       <c r="K34" t="n">
-        <v>-3.5</v>
+        <v>-6.2</v>
       </c>
       <c r="L34" t="n">
-        <v>65.64</v>
+        <v>70.02</v>
       </c>
       <c r="M34" t="n">
-        <v>3.99</v>
+        <v>1.34</v>
       </c>
       <c r="N34" t="n">
-        <v>39906048</v>
+        <v>13430794</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>39906048</v>
+        <v>13430794</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -8313,94 +8317,94 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>02-09-2026</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="W34" t="n">
+        <v>3156</v>
+      </c>
+      <c r="X34" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>200.11</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>191.8684857142857</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>Aging</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Mature Accumulation</t>
+        </is>
+      </c>
+      <c r="AN34" t="inlineStr">
+        <is>
+          <t>Mature — Wait for Pullback</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>31-08-2026</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>02-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ34" t="n">
         <v>2</v>
       </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>17-09-2026</t>
-        </is>
-      </c>
-      <c r="V34" t="n">
-        <v>0.233</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1716</v>
-      </c>
-      <c r="X34" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>-3</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AE34" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>36</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>172.69</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>183.55</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>-12</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>159.624192</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>16-09-2026</t>
-        </is>
-      </c>
-      <c r="AP34" t="inlineStr">
-        <is>
-          <t>17-09-2026</t>
-        </is>
-      </c>
-      <c r="AQ34" t="n">
-        <v>1</v>
-      </c>
       <c r="AR34" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="AS34" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="AT34" t="n">
         <v>0</v>
@@ -8409,67 +8413,67 @@
         <v>0</v>
       </c>
       <c r="AV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>13430794</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>13430794</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP34" t="n">
         <v>2</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>39906048</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>39906048</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>39906048</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO34" t="n">
-        <v>39906048</v>
-      </c>
-      <c r="BP34" t="n">
-        <v>1</v>
       </c>
       <c r="BQ34" t="n">
         <v>0</v>
@@ -8481,16 +8485,16 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>AVONMORE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ENVIRO INFRA ENGINEERS LIMITED</t>
+          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -8498,40 +8502,40 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F35" t="n">
         <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I35" t="n">
-        <v>180.96</v>
+        <v>12.3</v>
       </c>
       <c r="J35" t="n">
-        <v>191.87</v>
+        <v>12.86</v>
       </c>
       <c r="K35" t="n">
-        <v>-5.7</v>
+        <v>-4.4</v>
       </c>
       <c r="L35" t="n">
-        <v>70.02</v>
+        <v>69.12</v>
       </c>
       <c r="M35" t="n">
-        <v>1.34</v>
+        <v>2.35</v>
       </c>
       <c r="N35" t="n">
-        <v>13430794</v>
+        <v>23479616</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>13430794</v>
+        <v>23479616</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -8545,94 +8549,90 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="V35" t="n">
-        <v>0.042</v>
+        <v>0.679</v>
       </c>
       <c r="W35" t="n">
-        <v>3168</v>
+        <v>346</v>
       </c>
       <c r="X35" t="n">
-        <v>18.7</v>
+        <v>1115</v>
       </c>
       <c r="Y35" t="n">
-        <v>-4</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>51</v>
-      </c>
+        <v>-61</v>
+      </c>
+      <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="n">
-        <v>-9</v>
+        <v>-98</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.04</v>
+        <v>0.01</v>
       </c>
       <c r="AC35" t="n">
-        <v>20.8</v>
+        <v>2.46</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.15</v>
+        <v>0.44</v>
       </c>
       <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>21</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="n">
-        <v>200.83</v>
+        <v>12.77</v>
       </c>
       <c r="AH35" t="n">
-        <v>193.07</v>
+        <v>12.95</v>
       </c>
       <c r="AI35" t="n">
-        <v>9.6</v>
+        <v>-1.2</v>
       </c>
       <c r="AJ35" t="n">
-        <v>191.8684857142857</v>
+        <v>12.85608234597773</v>
       </c>
       <c r="AK35" t="n">
-        <v>-5.7</v>
+        <v>-4.3</v>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>Aging</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>Mature — Wait for Pullback</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>10-08-2026</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="AQ35" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="AR35" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="AS35" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="AT35" t="n">
         <v>0</v>
@@ -8641,13 +8641,13 @@
         <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AW35" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="AX35" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="AY35" t="n">
         <v>0</v>
@@ -8656,13 +8656,13 @@
         <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>5273610</v>
       </c>
       <c r="BB35" t="n">
-        <v>13430794</v>
+        <v>20093495</v>
       </c>
       <c r="BC35" t="n">
-        <v>13430794</v>
+        <v>23479616</v>
       </c>
       <c r="BD35" t="n">
         <v>0</v>
@@ -8698,10 +8698,10 @@
         <v>0</v>
       </c>
       <c r="BO35" t="n">
-        <v>0</v>
+        <v>5273610</v>
       </c>
       <c r="BP35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ35" t="n">
         <v>0</v>
@@ -8742,13 +8742,13 @@
         <v>-2</v>
       </c>
       <c r="I36" t="n">
-        <v>37.8</v>
+        <v>38.05</v>
       </c>
       <c r="J36" t="n">
         <v>42.6</v>
       </c>
       <c r="K36" t="n">
-        <v>-11.3</v>
+        <v>-10.7</v>
       </c>
       <c r="L36" t="n">
         <v>71.79000000000001</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>0.367</v>
+        <v>0.372</v>
       </c>
       <c r="W36" t="n">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="X36" t="n">
-        <v>94.3</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="Y36" t="n">
         <v>246</v>
@@ -8818,19 +8818,19 @@
         <v>4.21</v>
       </c>
       <c r="AG36" t="n">
-        <v>40.49</v>
+        <v>40.47</v>
       </c>
       <c r="AH36" t="n">
-        <v>39.75</v>
+        <v>39.74</v>
       </c>
       <c r="AI36" t="n">
-        <v>-3.5</v>
+        <v>-4.7</v>
       </c>
       <c r="AJ36" t="n">
         <v>42.60032805144139</v>
       </c>
       <c r="AK36" t="n">
-        <v>-11.3</v>
+        <v>-10.7</v>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
@@ -8974,13 +8974,13 @@
         <v>-16</v>
       </c>
       <c r="I37" t="n">
-        <v>424.05</v>
+        <v>427.2</v>
       </c>
       <c r="J37" t="n">
         <v>349.57</v>
       </c>
       <c r="K37" t="n">
-        <v>21.3</v>
+        <v>22.2</v>
       </c>
       <c r="L37" t="n">
         <v>70.55</v>
@@ -9017,10 +9017,10 @@
         </is>
       </c>
       <c r="V37" t="n">
-        <v>0.865</v>
+        <v>0.864</v>
       </c>
       <c r="W37" t="n">
-        <v>3653</v>
+        <v>3659</v>
       </c>
       <c r="X37" t="n">
         <v>25.6</v>
@@ -9050,19 +9050,19 @@
         <v>21</v>
       </c>
       <c r="AG37" t="n">
-        <v>442.49</v>
+        <v>442.44</v>
       </c>
       <c r="AH37" t="n">
-        <v>433.36</v>
+        <v>433.38</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="AJ37" t="n">
         <v>349.5746258337085</v>
       </c>
       <c r="AK37" t="n">
-        <v>21.3</v>
+        <v>22.2</v>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
@@ -9206,13 +9206,13 @@
         <v>-13</v>
       </c>
       <c r="I38" t="n">
-        <v>764.2</v>
+        <v>764.8</v>
       </c>
       <c r="J38" t="n">
         <v>726.25</v>
       </c>
       <c r="K38" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L38" t="n">
         <v>71.92</v>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>5232</v>
+        <v>5260</v>
       </c>
       <c r="X38" t="n">
         <v>12.3</v>
@@ -9282,19 +9282,19 @@
         <v>25</v>
       </c>
       <c r="AG38" t="n">
-        <v>703.1900000000001</v>
+        <v>706.3</v>
       </c>
       <c r="AH38" t="n">
-        <v>492.14</v>
+        <v>494.13</v>
       </c>
       <c r="AI38" t="n">
-        <v>139.1</v>
+        <v>126.6</v>
       </c>
       <c r="AJ38" t="n">
         <v>726.2520355006753</v>
       </c>
       <c r="AK38" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AL38" t="inlineStr">
         <is>
@@ -9438,13 +9438,13 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>191.89</v>
+        <v>194.47</v>
       </c>
       <c r="J39" t="n">
         <v>195.05</v>
       </c>
       <c r="K39" t="n">
-        <v>-1.6</v>
+        <v>-0.3</v>
       </c>
       <c r="L39" t="n">
         <v>60.6</v>
@@ -9484,7 +9484,7 @@
         <v>0.011</v>
       </c>
       <c r="W39" t="n">
-        <v>4154</v>
+        <v>4114</v>
       </c>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="n">
@@ -9512,19 +9512,19 @@
         <v>61</v>
       </c>
       <c r="AG39" t="n">
-        <v>190.61</v>
+        <v>190.9</v>
       </c>
       <c r="AH39" t="n">
-        <v>176.65</v>
+        <v>176.6</v>
       </c>
       <c r="AI39" t="n">
-        <v>28.6</v>
+        <v>27.8</v>
       </c>
       <c r="AJ39" t="n">
         <v>195.0500869565217</v>
       </c>
       <c r="AK39" t="n">
-        <v>-1.6</v>
+        <v>-0.3</v>
       </c>
       <c r="AL39" t="inlineStr">
         <is>
@@ -9668,13 +9668,13 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>23.71</v>
+        <v>24.76</v>
       </c>
       <c r="J40" t="n">
         <v>21.01</v>
       </c>
       <c r="K40" t="n">
-        <v>12.9</v>
+        <v>17.8</v>
       </c>
       <c r="L40" t="n">
         <v>70.87</v>
@@ -9711,13 +9711,13 @@
         </is>
       </c>
       <c r="V40" t="n">
-        <v>0.108</v>
+        <v>0.106</v>
       </c>
       <c r="W40" t="n">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="X40" t="n">
-        <v>7.38</v>
+        <v>7.58</v>
       </c>
       <c r="Y40" t="n">
         <v>118</v>
@@ -9740,19 +9740,19 @@
       </c>
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AH40" t="n">
-        <v>15.8</v>
+        <v>15.86</v>
       </c>
       <c r="AI40" t="n">
-        <v>79.09999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="AJ40" t="n">
         <v>21.00741139152052</v>
       </c>
       <c r="AK40" t="n">
-        <v>12.9</v>
+        <v>17.9</v>
       </c>
       <c r="AL40" t="inlineStr">
         <is>
@@ -9867,12 +9867,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HINDCON</t>
+          <t>CHEMBOND</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Hindcon Chemicals Limited</t>
+          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -9884,141 +9884,141 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F41" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G41" t="n">
         <v>25</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I41" t="n">
-        <v>29.95</v>
+        <v>189.25</v>
       </c>
       <c r="J41" t="n">
-        <v>23.55</v>
+        <v>170.45</v>
       </c>
       <c r="K41" t="n">
+        <v>11</v>
+      </c>
+      <c r="L41" t="n">
+        <v>67.54000000000001</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2560187</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2560187</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>03-09-2026</t>
+        </is>
+      </c>
+      <c r="V41" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="W41" t="n">
+        <v>254</v>
+      </c>
+      <c r="X41" t="n">
         <v>27.2</v>
       </c>
-      <c r="L41" t="n">
-        <v>68.34</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N41" t="n">
-        <v>2018403</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>2018403</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S41" t="b">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>17</v>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>23-09-2026</t>
-        </is>
-      </c>
-      <c r="V41" t="n">
-        <v>0.138</v>
-      </c>
-      <c r="W41" t="n">
-        <v>146</v>
-      </c>
-      <c r="X41" t="n">
-        <v>33.7</v>
-      </c>
       <c r="Y41" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="Z41" t="n">
-        <v>3.17</v>
+        <v>1.87</v>
       </c>
       <c r="AA41" t="n">
-        <v>7</v>
+        <v>-31</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.49</v>
+        <v>3.36</v>
       </c>
       <c r="AC41" t="n">
-        <v>8.76</v>
+        <v>4.96</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF41" t="n">
-        <v>14.87</v>
+        <v>2.97</v>
       </c>
       <c r="AG41" t="n">
-        <v>24.72</v>
+        <v>182.38</v>
       </c>
       <c r="AH41" t="n">
-        <v>22.86</v>
+        <v>164.81</v>
       </c>
       <c r="AI41" t="n">
-        <v>55.1</v>
+        <v>31.2</v>
       </c>
       <c r="AJ41" t="n">
-        <v>23.5472893358377</v>
+        <v>170.4518641810919</v>
       </c>
       <c r="AK41" t="n">
-        <v>27.2</v>
+        <v>11</v>
       </c>
       <c r="AL41" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="AQ41" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AR41" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AS41" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="AT41" t="n">
         <v>0</v>
@@ -10027,13 +10027,13 @@
         <v>0</v>
       </c>
       <c r="AV41" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AW41" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="AX41" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="AY41" t="n">
         <v>0</v>
@@ -10042,13 +10042,13 @@
         <v>0</v>
       </c>
       <c r="BA41" t="n">
-        <v>1351825</v>
+        <v>0</v>
       </c>
       <c r="BB41" t="n">
-        <v>2018403</v>
+        <v>2560187</v>
       </c>
       <c r="BC41" t="n">
-        <v>2018403</v>
+        <v>2560187</v>
       </c>
       <c r="BD41" t="n">
         <v>0</v>
@@ -10084,10 +10084,10 @@
         <v>0</v>
       </c>
       <c r="BO41" t="n">
-        <v>1351825</v>
+        <v>0</v>
       </c>
       <c r="BP41" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="BQ41" t="n">
         <v>0</v>
@@ -10099,158 +10099,158 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ASAHISONG</t>
+          <t>HINDCON</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ASAHI SONGWON COLORS LIMITED</t>
+          <t>Hindcon Chemicals Limited</t>
         </is>
       </c>
       <c r="C42" t="n">
+        <v>26</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F42" t="n">
+        <v>4</v>
+      </c>
+      <c r="G42" t="n">
         <v>25</v>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Avoid</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" t="n">
-        <v>15</v>
-      </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>28.46</v>
+      </c>
+      <c r="J42" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="K42" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="L42" t="n">
+        <v>68.34</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2018403</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2018403</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
         <v>17</v>
       </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>364.1</v>
-      </c>
-      <c r="J42" t="n">
-        <v>338.1</v>
-      </c>
-      <c r="K42" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="L42" t="n">
-        <v>66.73</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="N42" t="n">
-        <v>3381000</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>3381000</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S42" t="b">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>1</v>
-      </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
       <c r="V42" t="n">
-        <v>0.078</v>
+        <v>0.138</v>
       </c>
       <c r="W42" t="n">
-        <v>434</v>
+        <v>146</v>
       </c>
       <c r="X42" t="n">
-        <v>12.8</v>
+        <v>33.6</v>
       </c>
       <c r="Y42" t="n">
-        <v>-8</v>
+        <v>19</v>
       </c>
       <c r="Z42" t="n">
-        <v>24</v>
+        <v>3.17</v>
       </c>
       <c r="AA42" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="AB42" t="n">
-        <v>14.36</v>
+        <v>0.49</v>
       </c>
       <c r="AC42" t="n">
-        <v>9.94</v>
+        <v>8.76</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="AE42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>18</v>
+        <v>14.87</v>
       </c>
       <c r="AG42" t="n">
-        <v>370.81</v>
+        <v>24.83</v>
       </c>
       <c r="AH42" t="n">
-        <v>275.06</v>
+        <v>22.86</v>
       </c>
       <c r="AI42" t="n">
-        <v>58</v>
+        <v>22.8</v>
       </c>
       <c r="AJ42" t="n">
-        <v>338.1</v>
+        <v>23.5472893358377</v>
       </c>
       <c r="AK42" t="n">
-        <v>7.7</v>
+        <v>20.9</v>
       </c>
       <c r="AL42" t="inlineStr">
         <is>
-          <t>Aging</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>Mature — Wait for Pullback</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AR42" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="AS42" t="n">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="AT42" t="n">
         <v>0</v>
@@ -10259,13 +10259,13 @@
         <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AW42" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="AX42" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="AY42" t="n">
         <v>0</v>
@@ -10274,13 +10274,13 @@
         <v>0</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
+        <v>1351825</v>
       </c>
       <c r="BB42" t="n">
-        <v>3381000</v>
+        <v>2018403</v>
       </c>
       <c r="BC42" t="n">
-        <v>3381000</v>
+        <v>2018403</v>
       </c>
       <c r="BD42" t="n">
         <v>0</v>
@@ -10316,10 +10316,10 @@
         <v>0</v>
       </c>
       <c r="BO42" t="n">
-        <v>0</v>
+        <v>1351825</v>
       </c>
       <c r="BP42" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="BQ42" t="n">
         <v>0</v>
@@ -10331,124 +10331,124 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CHEMBOND</t>
+          <t>ASAHISONG</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
+          <t>ASAHI SONGWON COLORS LIMITED</t>
         </is>
       </c>
       <c r="C43" t="n">
+        <v>25</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>15</v>
+      </c>
+      <c r="G43" t="n">
+        <v>17</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>365.05</v>
+      </c>
+      <c r="J43" t="n">
+        <v>338.1</v>
+      </c>
+      <c r="K43" t="n">
+        <v>8</v>
+      </c>
+      <c r="L43" t="n">
+        <v>66.73</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="N43" t="n">
+        <v>3381000</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>3381000</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>11-08-2026</t>
+        </is>
+      </c>
+      <c r="V43" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="W43" t="n">
+        <v>432</v>
+      </c>
+      <c r="X43" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>-8</v>
+      </c>
+      <c r="Z43" t="n">
         <v>24</v>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Avoid</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>4</v>
-      </c>
-      <c r="F43" t="n">
-        <v>8</v>
-      </c>
-      <c r="G43" t="n">
-        <v>21</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I43" t="n">
-        <v>181.76</v>
-      </c>
-      <c r="J43" t="n">
-        <v>170.45</v>
-      </c>
-      <c r="K43" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="L43" t="n">
-        <v>67.54000000000001</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="N43" t="n">
-        <v>2560187</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>2560187</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S43" t="b">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2</v>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>03-09-2026</t>
-        </is>
-      </c>
-      <c r="V43" t="n">
-        <v>0.102</v>
-      </c>
-      <c r="W43" t="n">
-        <v>251</v>
-      </c>
-      <c r="X43" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AA43" t="n">
-        <v>-31</v>
+        <v>33</v>
       </c>
       <c r="AB43" t="n">
-        <v>3.36</v>
+        <v>14.36</v>
       </c>
       <c r="AC43" t="n">
-        <v>4.96</v>
+        <v>9.94</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="AE43" t="b">
         <v>1</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.97</v>
+        <v>18</v>
       </c>
       <c r="AG43" t="n">
-        <v>182.09</v>
+        <v>370.99</v>
       </c>
       <c r="AH43" t="n">
-        <v>164.68</v>
+        <v>275.33</v>
       </c>
       <c r="AI43" t="n">
-        <v>28</v>
+        <v>60.2</v>
       </c>
       <c r="AJ43" t="n">
-        <v>170.4518641810919</v>
+        <v>338.1</v>
       </c>
       <c r="AK43" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AL43" t="inlineStr">
         <is>
@@ -10467,22 +10467,22 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="AQ43" t="n">
         <v>0</v>
       </c>
       <c r="AR43" t="n">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="AS43" t="n">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="AT43" t="n">
         <v>0</v>
@@ -10494,10 +10494,10 @@
         <v>0</v>
       </c>
       <c r="AW43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY43" t="n">
         <v>0</v>
@@ -10509,10 +10509,10 @@
         <v>0</v>
       </c>
       <c r="BB43" t="n">
-        <v>2560187</v>
+        <v>3381000</v>
       </c>
       <c r="BC43" t="n">
-        <v>2560187</v>
+        <v>3381000</v>
       </c>
       <c r="BD43" t="n">
         <v>0</v>
@@ -10551,7 +10551,7 @@
         <v>0</v>
       </c>
       <c r="BP43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ43" t="n">
         <v>0</v>
@@ -10592,13 +10592,13 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>606.35</v>
+        <v>616.2</v>
       </c>
       <c r="J44" t="n">
         <v>622.4400000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>-2.6</v>
+        <v>-1</v>
       </c>
       <c r="L44" t="n">
         <v>74.02</v>
@@ -10638,7 +10638,7 @@
         <v>0.051</v>
       </c>
       <c r="W44" t="n">
-        <v>959</v>
+        <v>963</v>
       </c>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="n">
@@ -10666,19 +10666,19 @@
         <v>6</v>
       </c>
       <c r="AG44" t="n">
-        <v>599.48</v>
+        <v>599.9400000000001</v>
       </c>
       <c r="AH44" t="n">
-        <v>551.25</v>
+        <v>551.7</v>
       </c>
       <c r="AI44" t="n">
-        <v>25.6</v>
+        <v>22.1</v>
       </c>
       <c r="AJ44" t="n">
         <v>622.4351173945973</v>
       </c>
       <c r="AK44" t="n">
-        <v>-2.6</v>
+        <v>-1</v>
       </c>
       <c r="AL44" t="inlineStr">
         <is>
@@ -10822,13 +10822,13 @@
         <v>-19</v>
       </c>
       <c r="I45" t="n">
-        <v>1790.2</v>
+        <v>1752.2</v>
       </c>
       <c r="J45" t="n">
         <v>1579.83</v>
       </c>
       <c r="K45" t="n">
-        <v>13.3</v>
+        <v>10.9</v>
       </c>
       <c r="L45" t="n">
         <v>67.55</v>
@@ -10868,10 +10868,10 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>3662</v>
+        <v>3653</v>
       </c>
       <c r="X45" t="n">
-        <v>82.40000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="Y45" t="n">
         <v>42</v>
@@ -10898,19 +10898,19 @@
         <v>27</v>
       </c>
       <c r="AG45" t="n">
-        <v>1671.93</v>
+        <v>1676.07</v>
       </c>
       <c r="AH45" t="n">
-        <v>1398.64</v>
+        <v>1400.19</v>
       </c>
       <c r="AI45" t="n">
-        <v>58</v>
+        <v>42.7</v>
       </c>
       <c r="AJ45" t="n">
         <v>1579.830529039607</v>
       </c>
       <c r="AK45" t="n">
-        <v>13.3</v>
+        <v>10.9</v>
       </c>
       <c r="AL45" t="inlineStr">
         <is>
@@ -11054,13 +11054,13 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>262.95</v>
+        <v>266.7</v>
       </c>
       <c r="J46" t="n">
         <v>278.98</v>
       </c>
       <c r="K46" t="n">
-        <v>-5.7</v>
+        <v>-4.4</v>
       </c>
       <c r="L46" t="n">
         <v>73.72</v>
@@ -11100,7 +11100,7 @@
         <v>0.006</v>
       </c>
       <c r="W46" t="n">
-        <v>4840</v>
+        <v>4846</v>
       </c>
       <c r="X46" t="n">
         <v>12.5</v>
@@ -11126,19 +11126,19 @@
       </c>
       <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="n">
-        <v>294.79</v>
+        <v>293.62</v>
       </c>
       <c r="AH46" t="n">
-        <v>310.62</v>
+        <v>310.37</v>
       </c>
       <c r="AI46" t="n">
-        <v>-12.1</v>
+        <v>-14.4</v>
       </c>
       <c r="AJ46" t="n">
         <v>278.9837</v>
       </c>
       <c r="AK46" t="n">
-        <v>-5.7</v>
+        <v>-4.4</v>
       </c>
       <c r="AL46" t="inlineStr">
         <is>
@@ -11282,13 +11282,13 @@
         <v>-18</v>
       </c>
       <c r="I47" t="n">
-        <v>1010</v>
+        <v>1016.7</v>
       </c>
       <c r="J47" t="n">
         <v>1157.18</v>
       </c>
       <c r="K47" t="n">
-        <v>-12.7</v>
+        <v>-12.1</v>
       </c>
       <c r="L47" t="n">
         <v>61.21</v>
@@ -11328,10 +11328,10 @@
         <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>103529</v>
+        <v>103712</v>
       </c>
       <c r="X47" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="Y47" t="n">
         <v>18</v>
@@ -11358,19 +11358,19 @@
         <v>15</v>
       </c>
       <c r="AG47" t="n">
-        <v>1124.94</v>
+        <v>1123.5</v>
       </c>
       <c r="AH47" t="n">
-        <v>1136.75</v>
+        <v>1136.78</v>
       </c>
       <c r="AI47" t="n">
-        <v>-13.5</v>
+        <v>-16.2</v>
       </c>
       <c r="AJ47" t="n">
         <v>1157.177537688442</v>
       </c>
       <c r="AK47" t="n">
-        <v>-12.7</v>
+        <v>-12.1</v>
       </c>
       <c r="AL47" t="inlineStr">
         <is>
@@ -11514,13 +11514,13 @@
         <v>-1</v>
       </c>
       <c r="I48" t="n">
-        <v>104.78</v>
+        <v>101.24</v>
       </c>
       <c r="J48" t="n">
         <v>111.01</v>
       </c>
       <c r="K48" t="n">
-        <v>-5.6</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="L48" t="n">
         <v>73.48</v>
@@ -11557,13 +11557,13 @@
         </is>
       </c>
       <c r="V48" t="n">
-        <v>0.231</v>
+        <v>0.234</v>
       </c>
       <c r="W48" t="n">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="X48" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="Y48" t="n">
         <v>21</v>
@@ -11590,19 +11590,19 @@
         <v>4.11</v>
       </c>
       <c r="AG48" t="n">
-        <v>111.76</v>
+        <v>111.57</v>
       </c>
       <c r="AH48" t="n">
-        <v>117.51</v>
+        <v>117.33</v>
       </c>
       <c r="AI48" t="n">
-        <v>-6.3</v>
+        <v>-11.1</v>
       </c>
       <c r="AJ48" t="n">
         <v>111.0077475247525</v>
       </c>
       <c r="AK48" t="n">
-        <v>-5.6</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
@@ -11798,13 +11798,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>84.90000000000001</v>
+        <v>83.67</v>
       </c>
       <c r="D2" t="n">
         <v>77.33</v>
       </c>
       <c r="E2" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F2" t="n">
         <v>61.32</v>
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>801.3</v>
+        <v>795.9</v>
       </c>
       <c r="D3" t="n">
         <v>819.08</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.2</v>
+        <v>-2.8</v>
       </c>
       <c r="F3" t="n">
         <v>73</v>
@@ -11868,13 +11868,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>296.45</v>
+        <v>296.55</v>
       </c>
       <c r="D4" t="n">
         <v>265.56</v>
       </c>
       <c r="E4" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="F4" t="n">
         <v>64.63</v>
@@ -11903,13 +11903,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>899.9</v>
+        <v>899</v>
       </c>
       <c r="D5" t="n">
         <v>869.9299999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="F5" t="n">
         <v>61.71</v>
@@ -11938,13 +11938,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>534.75</v>
+        <v>533.85</v>
       </c>
       <c r="D6" t="n">
         <v>510.94</v>
       </c>
       <c r="E6" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="F6" t="n">
         <v>62.09</v>
@@ -11964,140 +11964,140 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>INDORAMA</t>
+          <t>SIGIND</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>INDO RAMA SYNTHETICS (INDIA) LIMITED</t>
+          <t>Signet Industries Limited</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>88.09999999999999</v>
+        <v>61.05</v>
       </c>
       <c r="D7" t="n">
-        <v>75.68000000000001</v>
+        <v>74.22</v>
       </c>
       <c r="E7" t="n">
-        <v>16.4</v>
+        <v>-17.7</v>
       </c>
       <c r="F7" t="n">
-        <v>74.84999999999999</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>3.14</v>
+        <v>2.01</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SIGIND</t>
+          <t>NURECA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Signet Industries Limited</t>
+          <t>NURECA LIMITED</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>58.16</v>
+        <v>331.65</v>
       </c>
       <c r="D8" t="n">
-        <v>74.22</v>
+        <v>333.11</v>
       </c>
       <c r="E8" t="n">
-        <v>-21.6</v>
+        <v>-0.4</v>
       </c>
       <c r="F8" t="n">
-        <v>72.56999999999999</v>
+        <v>63.24</v>
       </c>
       <c r="G8" t="n">
-        <v>2.01</v>
+        <v>3.75</v>
       </c>
       <c r="H8" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NURECA</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NURECA LIMITED</t>
+          <t>THANGAMAYIL JEWELLERY LIMITED</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>331.35</v>
+        <v>4889.5</v>
       </c>
       <c r="D9" t="n">
-        <v>333.11</v>
+        <v>5198.76</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5</v>
+        <v>-5.9</v>
       </c>
       <c r="F9" t="n">
-        <v>63.24</v>
+        <v>67.16</v>
       </c>
       <c r="G9" t="n">
-        <v>3.75</v>
+        <v>7.21</v>
       </c>
       <c r="H9" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>BMWVENTLTD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>THANGAMAYIL JEWELLERY LIMITED</t>
+          <t>BMW VENTURES LIMITED</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4810.5</v>
+        <v>57.95</v>
       </c>
       <c r="D10" t="n">
-        <v>5198.76</v>
+        <v>55.06</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.5</v>
+        <v>5.2</v>
       </c>
       <c r="F10" t="n">
-        <v>67.16</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>7.21</v>
+        <v>2.9</v>
       </c>
       <c r="H10" t="n">
         <v>6</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>22-09-2026</t>
         </is>
       </c>
     </row>
@@ -12113,13 +12113,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1044.7</v>
+        <v>1049.4</v>
       </c>
       <c r="D11" t="n">
         <v>1175.33</v>
       </c>
       <c r="E11" t="n">
-        <v>-11.1</v>
+        <v>-10.7</v>
       </c>
       <c r="F11" t="n">
         <v>69.75</v>
@@ -12139,136 +12139,136 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HEXAGON</t>
+          <t>INDORAMA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HEXAGON NUTRITION LIMITED</t>
+          <t>INDO RAMA SYNTHETICS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>68.59</v>
+        <v>92.39</v>
       </c>
       <c r="D12" t="n">
-        <v>64.48999999999999</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>6.4</v>
+        <v>22.1</v>
       </c>
       <c r="F12" t="n">
-        <v>64.29000000000001</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>0.57</v>
+        <v>3.14</v>
       </c>
       <c r="H12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BHAGERIA</t>
+          <t>HEXAGON</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bhageria Industries Limited</t>
+          <t>HEXAGON NUTRITION LIMITED</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>367</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>217.8</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>68.5</v>
+        <v>7.7</v>
       </c>
       <c r="F13" t="n">
-        <v>71.75</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>0.82</v>
+        <v>0.57</v>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>18-09-2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ALEMBICLTD</t>
+          <t>BHAGERIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Alembic Limited</t>
+          <t>Bhageria Industries Limited</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>99.72</v>
+        <v>364.9</v>
       </c>
       <c r="D14" t="n">
-        <v>96.81999999999999</v>
+        <v>217.8</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>67.5</v>
       </c>
       <c r="F14" t="n">
-        <v>70.88</v>
+        <v>71.75</v>
       </c>
       <c r="G14" t="n">
-        <v>14.28</v>
+        <v>0.82</v>
       </c>
       <c r="H14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SILVERTUC</t>
+          <t>ALEMBICLTD</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
+          <t>Alembic Limited</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>125.98</v>
+        <v>99.25</v>
       </c>
       <c r="D15" t="n">
-        <v>171.54</v>
+        <v>96.81999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>-26.6</v>
+        <v>2.5</v>
       </c>
       <c r="F15" t="n">
-        <v>74.59</v>
+        <v>70.88</v>
       </c>
       <c r="G15" t="n">
-        <v>1.11</v>
+        <v>14.28</v>
       </c>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -12279,280 +12279,280 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VEEGALAND</t>
+          <t>SILVERTUC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Veegaland Developers Limited</t>
+          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>136.9</v>
+        <v>131.18</v>
       </c>
       <c r="D16" t="n">
-        <v>143.72</v>
+        <v>171.54</v>
       </c>
       <c r="E16" t="n">
-        <v>-4.7</v>
+        <v>-23.5</v>
       </c>
       <c r="F16" t="n">
-        <v>63.69</v>
+        <v>74.59</v>
       </c>
       <c r="G16" t="n">
-        <v>19.68</v>
+        <v>1.11</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>22-09-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CHEMBONDCH</t>
+          <t>TAINWALCHM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CHEMBOND CHEMICALS LIMITED</t>
+          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>219.31</v>
+        <v>219.26</v>
       </c>
       <c r="D17" t="n">
-        <v>243.52</v>
+        <v>210.19</v>
       </c>
       <c r="E17" t="n">
-        <v>-9.9</v>
+        <v>4.3</v>
       </c>
       <c r="F17" t="n">
-        <v>67.65000000000001</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>1.11</v>
+        <v>0.62</v>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>28-09-2026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>JAYAGROGN</t>
+          <t>VEEGALAND</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Jayant Agro-Organics Limited</t>
+          <t>Veegaland Developers Limited</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>208.96</v>
+        <v>133.9</v>
       </c>
       <c r="D18" t="n">
-        <v>232.74</v>
+        <v>143.72</v>
       </c>
       <c r="E18" t="n">
-        <v>-10.2</v>
+        <v>-6.8</v>
       </c>
       <c r="F18" t="n">
-        <v>67.13</v>
+        <v>63.69</v>
       </c>
       <c r="G18" t="n">
-        <v>0.57</v>
+        <v>19.68</v>
       </c>
       <c r="H18" t="n">
         <v>4</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>22-09-2026</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BERGEPAINT</t>
+          <t>CHEMBONDCH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BERGER PAINTS (I) LIMITED</t>
+          <t>CHEMBOND CHEMICALS LIMITED</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>467.95</v>
+        <v>220.86</v>
       </c>
       <c r="D19" t="n">
-        <v>489.56</v>
+        <v>243.52</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>75</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>4.84</v>
+        <v>1.11</v>
       </c>
       <c r="H19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>07-09-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BMWVENTLTD</t>
+          <t>JAYAGROGN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BMW VENTURES LIMITED</t>
+          <t>Jayant Agro-Organics Limited</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>49.72</v>
+        <v>212.86</v>
       </c>
       <c r="D20" t="n">
-        <v>55.06</v>
+        <v>232.74</v>
       </c>
       <c r="E20" t="n">
-        <v>-9.699999999999999</v>
+        <v>-8.5</v>
       </c>
       <c r="F20" t="n">
-        <v>73.01000000000001</v>
+        <v>67.13</v>
       </c>
       <c r="G20" t="n">
-        <v>2.9</v>
+        <v>0.57</v>
       </c>
       <c r="H20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>22-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HTEL</t>
+          <t>BERGEPAINT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers Limited</t>
+          <t>BERGER PAINTS (I) LIMITED</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>97.27</v>
+        <v>471.9</v>
       </c>
       <c r="D21" t="n">
-        <v>68.68000000000001</v>
+        <v>489.56</v>
       </c>
       <c r="E21" t="n">
-        <v>41.6</v>
+        <v>-3.6</v>
       </c>
       <c r="F21" t="n">
-        <v>71.22</v>
+        <v>75</v>
       </c>
       <c r="G21" t="n">
-        <v>0.86</v>
+        <v>4.84</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SRGHFL</t>
+          <t>HTEL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SRG HOUSING FINANCE LIMITED</t>
+          <t>Hy-Tech Engineers Limited</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>120.97</v>
+        <v>90.37</v>
       </c>
       <c r="D22" t="n">
-        <v>132.2</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>-8.5</v>
+        <v>31.6</v>
       </c>
       <c r="F22" t="n">
-        <v>67.83</v>
+        <v>71.22</v>
       </c>
       <c r="G22" t="n">
-        <v>1.98</v>
+        <v>0.86</v>
       </c>
       <c r="H22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TAINWALCHM</t>
+          <t>SRGHFL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
+          <t>SRG HOUSING FINANCE LIMITED</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>203.35</v>
+        <v>115.81</v>
       </c>
       <c r="D23" t="n">
-        <v>210.19</v>
+        <v>132.2</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3</v>
+        <v>-12.4</v>
       </c>
       <c r="F23" t="n">
-        <v>67.04000000000001</v>
+        <v>67.83</v>
       </c>
       <c r="G23" t="n">
-        <v>0.62</v>
+        <v>1.98</v>
       </c>
       <c r="H23" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>28-09-2026</t>
+          <t>16-09-2026</t>
         </is>
       </c>
     </row>
@@ -12568,13 +12568,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>567.75</v>
+        <v>545.25</v>
       </c>
       <c r="D24" t="n">
         <v>638.11</v>
       </c>
       <c r="E24" t="n">
-        <v>-11</v>
+        <v>-14.6</v>
       </c>
       <c r="F24" t="n">
         <v>64.68000000000001</v>
@@ -12594,66 +12594,66 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SINCLAIR</t>
+          <t>WCIL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SINCLAIRS HOTELS LIMITED</t>
+          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>74.83</v>
+        <v>97.52</v>
       </c>
       <c r="D25" t="n">
-        <v>81.09999999999999</v>
+        <v>96.03</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.7</v>
+        <v>1.6</v>
       </c>
       <c r="F25" t="n">
-        <v>62.78</v>
+        <v>71.89</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="H25" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AFFORDABLE</t>
+          <t>SINCLAIR</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AFFORDABLE ROBOTIC &amp; AUTOMATION LIMITED</t>
+          <t>SINCLAIRS HOTELS LIMITED</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>158.28</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>174.27</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>-9.199999999999999</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>61.48</v>
+        <v>62.78</v>
       </c>
       <c r="G26" t="n">
-        <v>1.07</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -12673,13 +12673,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>150.66</v>
+        <v>152.08</v>
       </c>
       <c r="D27" t="n">
         <v>166</v>
       </c>
       <c r="E27" t="n">
-        <v>-9.199999999999999</v>
+        <v>-8.4</v>
       </c>
       <c r="F27" t="n">
         <v>64.08</v>
@@ -12708,13 +12708,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>416</v>
+        <v>414.5</v>
       </c>
       <c r="D28" t="n">
         <v>417.34</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.3</v>
+        <v>-0.7</v>
       </c>
       <c r="F28" t="n">
         <v>61.75</v>
@@ -12734,66 +12734,66 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>WCIL</t>
+          <t>OBCL</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
+          <t>OBCL LIMITED</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>93.3</v>
+        <v>55.19</v>
       </c>
       <c r="D29" t="n">
-        <v>96.03</v>
+        <v>54.07</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.8</v>
+        <v>2.1</v>
       </c>
       <c r="F29" t="n">
-        <v>71.89</v>
+        <v>67.23</v>
       </c>
       <c r="G29" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="H29" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>OBCL</t>
+          <t>AFFORDABLE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>OBCL LIMITED</t>
+          <t>AFFORDABLE ROBOTIC &amp; AUTOMATION LIMITED</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>54.84</v>
+        <v>159.8</v>
       </c>
       <c r="D30" t="n">
-        <v>54.07</v>
+        <v>174.27</v>
       </c>
       <c r="E30" t="n">
-        <v>1.4</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>67.23</v>
+        <v>61.48</v>
       </c>
       <c r="G30" t="n">
-        <v>2.2</v>
+        <v>1.07</v>
       </c>
       <c r="H30" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -12813,13 +12813,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="D31" t="n">
         <v>2.82</v>
       </c>
       <c r="E31" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="F31" t="n">
         <v>64.45</v>
@@ -12839,140 +12839,140 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AVONMORE</t>
+          <t>TIGERLOGS</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
+          <t>Tiger Logistics (India) Limited</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>12.43</v>
+        <v>23.59</v>
       </c>
       <c r="D32" t="n">
-        <v>12.86</v>
+        <v>27.53</v>
       </c>
       <c r="E32" t="n">
-        <v>-3.3</v>
+        <v>-14.3</v>
       </c>
       <c r="F32" t="n">
-        <v>69.12</v>
+        <v>61.81</v>
       </c>
       <c r="G32" t="n">
-        <v>2.35</v>
+        <v>0.65</v>
       </c>
       <c r="H32" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TIGERLOGS</t>
+          <t>LAOPALA</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tiger Logistics (India) Limited</t>
+          <t>LA OPALA RG LIMITED</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>24.88</v>
+        <v>154.76</v>
       </c>
       <c r="D33" t="n">
-        <v>27.53</v>
+        <v>159.62</v>
       </c>
       <c r="E33" t="n">
-        <v>-9.6</v>
+        <v>-3</v>
       </c>
       <c r="F33" t="n">
-        <v>61.81</v>
+        <v>65.64</v>
       </c>
       <c r="G33" t="n">
-        <v>0.65</v>
+        <v>3.99</v>
       </c>
       <c r="H33" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>LAOPALA</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LA OPALA RG LIMITED</t>
+          <t>ENVIRO INFRA ENGINEERS LIMITED</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>153.98</v>
+        <v>179.96</v>
       </c>
       <c r="D34" t="n">
-        <v>159.62</v>
+        <v>191.87</v>
       </c>
       <c r="E34" t="n">
-        <v>-3.5</v>
+        <v>-6.2</v>
       </c>
       <c r="F34" t="n">
-        <v>65.64</v>
+        <v>70.02</v>
       </c>
       <c r="G34" t="n">
-        <v>3.99</v>
+        <v>1.34</v>
       </c>
       <c r="H34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>17-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>AVONMORE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ENVIRO INFRA ENGINEERS LIMITED</t>
+          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>180.96</v>
+        <v>12.3</v>
       </c>
       <c r="D35" t="n">
-        <v>191.87</v>
+        <v>12.86</v>
       </c>
       <c r="E35" t="n">
-        <v>-5.7</v>
+        <v>-4.4</v>
       </c>
       <c r="F35" t="n">
-        <v>70.02</v>
+        <v>69.12</v>
       </c>
       <c r="G35" t="n">
-        <v>1.34</v>
+        <v>2.35</v>
       </c>
       <c r="H35" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
     </row>
@@ -12988,13 +12988,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>37.8</v>
+        <v>38.05</v>
       </c>
       <c r="D36" t="n">
         <v>42.6</v>
       </c>
       <c r="E36" t="n">
-        <v>-11.3</v>
+        <v>-10.7</v>
       </c>
       <c r="F36" t="n">
         <v>71.79000000000001</v>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>424.05</v>
+        <v>427.2</v>
       </c>
       <c r="D37" t="n">
         <v>349.57</v>
       </c>
       <c r="E37" t="n">
-        <v>21.3</v>
+        <v>22.2</v>
       </c>
       <c r="F37" t="n">
         <v>70.55</v>
@@ -13058,13 +13058,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>764.2</v>
+        <v>764.8</v>
       </c>
       <c r="D38" t="n">
         <v>726.25</v>
       </c>
       <c r="E38" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="F38" t="n">
         <v>71.92</v>
@@ -13093,13 +13093,13 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>191.89</v>
+        <v>194.47</v>
       </c>
       <c r="D39" t="n">
         <v>195.05</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.6</v>
+        <v>-0.3</v>
       </c>
       <c r="F39" t="n">
         <v>60.6</v>
@@ -13128,13 +13128,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>23.71</v>
+        <v>24.76</v>
       </c>
       <c r="D40" t="n">
         <v>21.01</v>
       </c>
       <c r="E40" t="n">
-        <v>12.9</v>
+        <v>17.8</v>
       </c>
       <c r="F40" t="n">
         <v>70.87</v>
@@ -13154,105 +13154,105 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HINDCON</t>
+          <t>CHEMBOND</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Hindcon Chemicals Limited</t>
+          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>29.95</v>
+        <v>189.25</v>
       </c>
       <c r="D41" t="n">
-        <v>23.55</v>
+        <v>170.45</v>
       </c>
       <c r="E41" t="n">
-        <v>27.2</v>
+        <v>11</v>
       </c>
       <c r="F41" t="n">
-        <v>68.34</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="G41" t="n">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="H41" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ASAHISONG</t>
+          <t>HINDCON</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ASAHI SONGWON COLORS LIMITED</t>
+          <t>Hindcon Chemicals Limited</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>364.1</v>
+        <v>28.46</v>
       </c>
       <c r="D42" t="n">
-        <v>338.1</v>
+        <v>23.55</v>
       </c>
       <c r="E42" t="n">
-        <v>7.7</v>
+        <v>20.8</v>
       </c>
       <c r="F42" t="n">
-        <v>66.73</v>
+        <v>68.34</v>
       </c>
       <c r="G42" t="n">
-        <v>0.34</v>
+        <v>0.2</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CHEMBOND</t>
+          <t>ASAHISONG</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
+          <t>ASAHI SONGWON COLORS LIMITED</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>181.76</v>
+        <v>365.05</v>
       </c>
       <c r="D43" t="n">
-        <v>170.45</v>
+        <v>338.1</v>
       </c>
       <c r="E43" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="F43" t="n">
-        <v>67.54000000000001</v>
+        <v>66.73</v>
       </c>
       <c r="G43" t="n">
-        <v>0.26</v>
+        <v>0.34</v>
       </c>
       <c r="H43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
     </row>
@@ -13268,13 +13268,13 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>606.35</v>
+        <v>616.2</v>
       </c>
       <c r="D44" t="n">
         <v>622.4400000000001</v>
       </c>
       <c r="E44" t="n">
-        <v>-2.6</v>
+        <v>-1</v>
       </c>
       <c r="F44" t="n">
         <v>74.02</v>
@@ -13303,13 +13303,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1790.2</v>
+        <v>1752.2</v>
       </c>
       <c r="D45" t="n">
         <v>1579.83</v>
       </c>
       <c r="E45" t="n">
-        <v>13.3</v>
+        <v>10.9</v>
       </c>
       <c r="F45" t="n">
         <v>67.55</v>
@@ -13338,13 +13338,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>262.95</v>
+        <v>266.7</v>
       </c>
       <c r="D46" t="n">
         <v>278.98</v>
       </c>
       <c r="E46" t="n">
-        <v>-5.7</v>
+        <v>-4.4</v>
       </c>
       <c r="F46" t="n">
         <v>73.72</v>
@@ -13373,13 +13373,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1010</v>
+        <v>1016.7</v>
       </c>
       <c r="D47" t="n">
         <v>1157.18</v>
       </c>
       <c r="E47" t="n">
-        <v>-12.7</v>
+        <v>-12.1</v>
       </c>
       <c r="F47" t="n">
         <v>61.21</v>
@@ -13408,13 +13408,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>104.78</v>
+        <v>101.24</v>
       </c>
       <c r="D48" t="n">
         <v>111.01</v>
       </c>
       <c r="E48" t="n">
-        <v>-5.6</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="F48" t="n">
         <v>73.48</v>
@@ -13464,7 +13464,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -13474,7 +13474,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -13504,7 +13504,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -13514,7 +13514,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
@@ -13534,7 +13534,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
